--- a/app/agents/core_agents/template/탬플릿_WBS.xlsx
+++ b/app/agents/core_agents/template/탬플릿_WBS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10910"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F9616B-DEB5-054B-BA77-7361448BCDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712255FA-ACCE-A947-A16F-B8F33C95C209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1020" yWindow="740" windowWidth="27780" windowHeight="13780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -247,6 +247,9 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -534,7 +537,7 @@
     <col min="1" max="1" width="7.83203125" style="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.1640625" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="85.5" style="6" customWidth="1"/>
     <col min="5" max="6" width="12.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="30.83203125" style="6" bestFit="1" customWidth="1"/>
@@ -586,7 +589,7 @@
       <c r="A2" s="7"/>
       <c r="B2" s="8"/>
       <c r="C2" s="9"/>
-      <c r="D2" s="15"/>
+      <c r="D2" s="16"/>
       <c r="E2" s="10"/>
       <c r="F2" s="10"/>
       <c r="G2" s="11"/>
@@ -600,7 +603,7 @@
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="9"/>
-      <c r="D3" s="15"/>
+      <c r="D3" s="16"/>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
       <c r="G3" s="11"/>
@@ -614,7 +617,7 @@
       <c r="A4" s="7"/>
       <c r="B4" s="8"/>
       <c r="C4" s="9"/>
-      <c r="D4" s="15"/>
+      <c r="D4" s="16"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="11"/>
@@ -628,7 +631,7 @@
       <c r="A5" s="7"/>
       <c r="B5" s="8"/>
       <c r="C5" s="9"/>
-      <c r="D5" s="15"/>
+      <c r="D5" s="16"/>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
       <c r="G5" s="11"/>
@@ -642,7 +645,7 @@
       <c r="A6" s="7"/>
       <c r="B6" s="8"/>
       <c r="C6" s="9"/>
-      <c r="D6" s="15"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="10"/>
       <c r="F6" s="10"/>
       <c r="G6" s="11"/>
@@ -656,7 +659,7 @@
       <c r="A7" s="7"/>
       <c r="B7" s="8"/>
       <c r="C7" s="9"/>
-      <c r="D7" s="15"/>
+      <c r="D7" s="16"/>
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
       <c r="G7" s="11"/>
@@ -670,7 +673,7 @@
       <c r="A8" s="7"/>
       <c r="B8" s="8"/>
       <c r="C8" s="9"/>
-      <c r="D8" s="15"/>
+      <c r="D8" s="16"/>
       <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="G8" s="11"/>
@@ -684,7 +687,7 @@
       <c r="A9" s="7"/>
       <c r="B9" s="8"/>
       <c r="C9" s="9"/>
-      <c r="D9" s="15"/>
+      <c r="D9" s="16"/>
       <c r="E9" s="10"/>
       <c r="F9" s="10"/>
       <c r="G9" s="11"/>
@@ -698,7 +701,7 @@
       <c r="A10" s="7"/>
       <c r="B10" s="8"/>
       <c r="C10" s="9"/>
-      <c r="D10" s="15"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
       <c r="G10" s="11"/>
@@ -712,7 +715,7 @@
       <c r="A11" s="7"/>
       <c r="B11" s="8"/>
       <c r="C11" s="9"/>
-      <c r="D11" s="15"/>
+      <c r="D11" s="16"/>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
       <c r="G11" s="11"/>
@@ -726,7 +729,7 @@
       <c r="A12" s="7"/>
       <c r="B12" s="8"/>
       <c r="C12" s="9"/>
-      <c r="D12" s="15"/>
+      <c r="D12" s="16"/>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="11"/>
@@ -740,7 +743,7 @@
       <c r="A13" s="7"/>
       <c r="B13" s="8"/>
       <c r="C13" s="9"/>
-      <c r="D13" s="15"/>
+      <c r="D13" s="16"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="11"/>
@@ -754,7 +757,7 @@
       <c r="A14" s="7"/>
       <c r="B14" s="8"/>
       <c r="C14" s="9"/>
-      <c r="D14" s="15"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="11"/>
@@ -768,7 +771,7 @@
       <c r="A15" s="7"/>
       <c r="B15" s="8"/>
       <c r="C15" s="9"/>
-      <c r="D15" s="15"/>
+      <c r="D15" s="16"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
       <c r="G15" s="11"/>
@@ -782,7 +785,7 @@
       <c r="A16" s="7"/>
       <c r="B16" s="8"/>
       <c r="C16" s="9"/>
-      <c r="D16" s="15"/>
+      <c r="D16" s="16"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
       <c r="G16" s="11"/>
@@ -796,7 +799,7 @@
       <c r="A17" s="7"/>
       <c r="B17" s="8"/>
       <c r="C17" s="9"/>
-      <c r="D17" s="15"/>
+      <c r="D17" s="16"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="11"/>
@@ -810,7 +813,7 @@
       <c r="A18" s="7"/>
       <c r="B18" s="8"/>
       <c r="C18" s="9"/>
-      <c r="D18" s="15"/>
+      <c r="D18" s="16"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
       <c r="G18" s="11"/>
@@ -824,7 +827,7 @@
       <c r="A19" s="7"/>
       <c r="B19" s="8"/>
       <c r="C19" s="9"/>
-      <c r="D19" s="15"/>
+      <c r="D19" s="16"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
       <c r="G19" s="11"/>
@@ -838,7 +841,7 @@
       <c r="A20" s="7"/>
       <c r="B20" s="8"/>
       <c r="C20" s="9"/>
-      <c r="D20" s="15"/>
+      <c r="D20" s="16"/>
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
       <c r="G20" s="11"/>
@@ -852,7 +855,7 @@
       <c r="A21" s="7"/>
       <c r="B21" s="8"/>
       <c r="C21" s="9"/>
-      <c r="D21" s="15"/>
+      <c r="D21" s="16"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="11"/>
@@ -866,7 +869,7 @@
       <c r="A22" s="7"/>
       <c r="B22" s="8"/>
       <c r="C22" s="9"/>
-      <c r="D22" s="15"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
       <c r="G22" s="11"/>
@@ -880,7 +883,7 @@
       <c r="A23" s="7"/>
       <c r="B23" s="8"/>
       <c r="C23" s="9"/>
-      <c r="D23" s="15"/>
+      <c r="D23" s="16"/>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="11"/>
@@ -894,7 +897,7 @@
       <c r="A24" s="7"/>
       <c r="B24" s="8"/>
       <c r="C24" s="9"/>
-      <c r="D24" s="15"/>
+      <c r="D24" s="16"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="11"/>
@@ -908,7 +911,7 @@
       <c r="A25" s="7"/>
       <c r="B25" s="8"/>
       <c r="C25" s="9"/>
-      <c r="D25" s="15"/>
+      <c r="D25" s="16"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="11"/>
@@ -922,7 +925,7 @@
       <c r="A26" s="7"/>
       <c r="B26" s="8"/>
       <c r="C26" s="9"/>
-      <c r="D26" s="15"/>
+      <c r="D26" s="16"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="11"/>
@@ -936,7 +939,7 @@
       <c r="A27" s="7"/>
       <c r="B27" s="8"/>
       <c r="C27" s="9"/>
-      <c r="D27" s="15"/>
+      <c r="D27" s="16"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="11"/>
@@ -950,7 +953,7 @@
       <c r="A28" s="7"/>
       <c r="B28" s="8"/>
       <c r="C28" s="9"/>
-      <c r="D28" s="15"/>
+      <c r="D28" s="16"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="11"/>
@@ -964,7 +967,7 @@
       <c r="A29" s="7"/>
       <c r="B29" s="8"/>
       <c r="C29" s="9"/>
-      <c r="D29" s="15"/>
+      <c r="D29" s="16"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="11"/>
@@ -978,7 +981,7 @@
       <c r="A30" s="7"/>
       <c r="B30" s="8"/>
       <c r="C30" s="9"/>
-      <c r="D30" s="15"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
       <c r="G30" s="11"/>
@@ -992,7 +995,7 @@
       <c r="A31" s="7"/>
       <c r="B31" s="8"/>
       <c r="C31" s="9"/>
-      <c r="D31" s="15"/>
+      <c r="D31" s="16"/>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="11"/>
@@ -1006,7 +1009,7 @@
       <c r="A32" s="7"/>
       <c r="B32" s="8"/>
       <c r="C32" s="9"/>
-      <c r="D32" s="15"/>
+      <c r="D32" s="16"/>
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="11"/>
@@ -1020,7 +1023,7 @@
       <c r="A33" s="7"/>
       <c r="B33" s="8"/>
       <c r="C33" s="9"/>
-      <c r="D33" s="15"/>
+      <c r="D33" s="16"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="11"/>
@@ -1034,7 +1037,7 @@
       <c r="A34" s="7"/>
       <c r="B34" s="8"/>
       <c r="C34" s="9"/>
-      <c r="D34" s="15"/>
+      <c r="D34" s="16"/>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
       <c r="G34" s="11"/>
@@ -1048,7 +1051,7 @@
       <c r="A35" s="7"/>
       <c r="B35" s="8"/>
       <c r="C35" s="9"/>
-      <c r="D35" s="15"/>
+      <c r="D35" s="16"/>
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
       <c r="G35" s="11"/>
@@ -1062,7 +1065,7 @@
       <c r="A36" s="7"/>
       <c r="B36" s="8"/>
       <c r="C36" s="9"/>
-      <c r="D36" s="15"/>
+      <c r="D36" s="16"/>
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
       <c r="G36" s="11"/>
@@ -1076,7 +1079,7 @@
       <c r="A37" s="7"/>
       <c r="B37" s="8"/>
       <c r="C37" s="9"/>
-      <c r="D37" s="15"/>
+      <c r="D37" s="16"/>
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
       <c r="G37" s="11"/>
@@ -1090,7 +1093,7 @@
       <c r="A38" s="7"/>
       <c r="B38" s="8"/>
       <c r="C38" s="9"/>
-      <c r="D38" s="15"/>
+      <c r="D38" s="16"/>
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
       <c r="G38" s="11"/>
@@ -1104,7 +1107,7 @@
       <c r="A39" s="7"/>
       <c r="B39" s="8"/>
       <c r="C39" s="9"/>
-      <c r="D39" s="15"/>
+      <c r="D39" s="16"/>
       <c r="E39" s="10"/>
       <c r="F39" s="10"/>
       <c r="G39" s="11"/>
@@ -1118,7 +1121,7 @@
       <c r="A40" s="7"/>
       <c r="B40" s="8"/>
       <c r="C40" s="9"/>
-      <c r="D40" s="15"/>
+      <c r="D40" s="16"/>
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
       <c r="G40" s="11"/>
@@ -1132,7 +1135,7 @@
       <c r="A41" s="7"/>
       <c r="B41" s="8"/>
       <c r="C41" s="9"/>
-      <c r="D41" s="15"/>
+      <c r="D41" s="16"/>
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
       <c r="G41" s="11"/>
@@ -1146,7 +1149,7 @@
       <c r="A42" s="7"/>
       <c r="B42" s="8"/>
       <c r="C42" s="9"/>
-      <c r="D42" s="15"/>
+      <c r="D42" s="16"/>
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
       <c r="G42" s="11"/>
@@ -1160,7 +1163,7 @@
       <c r="A43" s="7"/>
       <c r="B43" s="8"/>
       <c r="C43" s="9"/>
-      <c r="D43" s="15"/>
+      <c r="D43" s="16"/>
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
       <c r="G43" s="11"/>
@@ -1174,7 +1177,7 @@
       <c r="A44" s="7"/>
       <c r="B44" s="8"/>
       <c r="C44" s="9"/>
-      <c r="D44" s="15"/>
+      <c r="D44" s="16"/>
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
       <c r="G44" s="11"/>
@@ -1188,7 +1191,7 @@
       <c r="A45" s="7"/>
       <c r="B45" s="8"/>
       <c r="C45" s="9"/>
-      <c r="D45" s="15"/>
+      <c r="D45" s="16"/>
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
       <c r="G45" s="11"/>
@@ -1202,7 +1205,7 @@
       <c r="A46" s="7"/>
       <c r="B46" s="8"/>
       <c r="C46" s="9"/>
-      <c r="D46" s="15"/>
+      <c r="D46" s="16"/>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
       <c r="G46" s="11"/>
@@ -1216,7 +1219,7 @@
       <c r="A47" s="7"/>
       <c r="B47" s="8"/>
       <c r="C47" s="9"/>
-      <c r="D47" s="15"/>
+      <c r="D47" s="16"/>
       <c r="E47" s="10"/>
       <c r="F47" s="10"/>
       <c r="G47" s="11"/>
@@ -1230,7 +1233,7 @@
       <c r="A48" s="7"/>
       <c r="B48" s="8"/>
       <c r="C48" s="9"/>
-      <c r="D48" s="15"/>
+      <c r="D48" s="16"/>
       <c r="E48" s="10"/>
       <c r="F48" s="10"/>
       <c r="G48" s="11"/>
@@ -1244,7 +1247,7 @@
       <c r="A49" s="7"/>
       <c r="B49" s="8"/>
       <c r="C49" s="9"/>
-      <c r="D49" s="15"/>
+      <c r="D49" s="16"/>
       <c r="E49" s="10"/>
       <c r="F49" s="10"/>
       <c r="G49" s="11"/>
@@ -1258,7 +1261,7 @@
       <c r="A50" s="7"/>
       <c r="B50" s="8"/>
       <c r="C50" s="9"/>
-      <c r="D50" s="15"/>
+      <c r="D50" s="16"/>
       <c r="E50" s="10"/>
       <c r="F50" s="10"/>
       <c r="G50" s="11"/>
@@ -1272,7 +1275,7 @@
       <c r="A51" s="7"/>
       <c r="B51" s="8"/>
       <c r="C51" s="9"/>
-      <c r="D51" s="15"/>
+      <c r="D51" s="16"/>
       <c r="E51" s="10"/>
       <c r="F51" s="10"/>
       <c r="G51" s="11"/>
@@ -1286,7 +1289,7 @@
       <c r="A52" s="7"/>
       <c r="B52" s="8"/>
       <c r="C52" s="9"/>
-      <c r="D52" s="15"/>
+      <c r="D52" s="16"/>
       <c r="E52" s="10"/>
       <c r="F52" s="10"/>
       <c r="G52" s="11"/>
@@ -1300,7 +1303,7 @@
       <c r="A53" s="7"/>
       <c r="B53" s="8"/>
       <c r="C53" s="9"/>
-      <c r="D53" s="15"/>
+      <c r="D53" s="16"/>
       <c r="E53" s="10"/>
       <c r="F53" s="10"/>
       <c r="G53" s="11"/>
@@ -1314,7 +1317,7 @@
       <c r="A54" s="7"/>
       <c r="B54" s="8"/>
       <c r="C54" s="9"/>
-      <c r="D54" s="15"/>
+      <c r="D54" s="16"/>
       <c r="E54" s="10"/>
       <c r="F54" s="10"/>
       <c r="G54" s="11"/>
@@ -1328,7 +1331,7 @@
       <c r="A55" s="7"/>
       <c r="B55" s="8"/>
       <c r="C55" s="9"/>
-      <c r="D55" s="15"/>
+      <c r="D55" s="16"/>
       <c r="E55" s="10"/>
       <c r="F55" s="10"/>
       <c r="G55" s="11"/>
@@ -1342,7 +1345,7 @@
       <c r="A56" s="7"/>
       <c r="B56" s="8"/>
       <c r="C56" s="9"/>
-      <c r="D56" s="15"/>
+      <c r="D56" s="16"/>
       <c r="E56" s="10"/>
       <c r="F56" s="10"/>
       <c r="G56" s="11"/>
@@ -1356,7 +1359,7 @@
       <c r="A57" s="7"/>
       <c r="B57" s="8"/>
       <c r="C57" s="9"/>
-      <c r="D57" s="15"/>
+      <c r="D57" s="16"/>
       <c r="E57" s="10"/>
       <c r="F57" s="10"/>
       <c r="G57" s="11"/>
@@ -1370,7 +1373,7 @@
       <c r="A58" s="7"/>
       <c r="B58" s="8"/>
       <c r="C58" s="9"/>
-      <c r="D58" s="15"/>
+      <c r="D58" s="16"/>
       <c r="E58" s="10"/>
       <c r="F58" s="10"/>
       <c r="G58" s="11"/>
@@ -1384,7 +1387,7 @@
       <c r="A59" s="7"/>
       <c r="B59" s="8"/>
       <c r="C59" s="9"/>
-      <c r="D59" s="15"/>
+      <c r="D59" s="16"/>
       <c r="E59" s="10"/>
       <c r="F59" s="10"/>
       <c r="G59" s="11"/>
@@ -1398,7 +1401,7 @@
       <c r="A60" s="7"/>
       <c r="B60" s="8"/>
       <c r="C60" s="9"/>
-      <c r="D60" s="15"/>
+      <c r="D60" s="16"/>
       <c r="E60" s="10"/>
       <c r="F60" s="10"/>
       <c r="G60" s="11"/>
@@ -1412,7 +1415,7 @@
       <c r="A61" s="7"/>
       <c r="B61" s="8"/>
       <c r="C61" s="9"/>
-      <c r="D61" s="15"/>
+      <c r="D61" s="16"/>
       <c r="E61" s="10"/>
       <c r="F61" s="10"/>
       <c r="G61" s="11"/>
@@ -1426,7 +1429,7 @@
       <c r="A62" s="7"/>
       <c r="B62" s="8"/>
       <c r="C62" s="9"/>
-      <c r="D62" s="15"/>
+      <c r="D62" s="16"/>
       <c r="E62" s="10"/>
       <c r="F62" s="10"/>
       <c r="G62" s="11"/>
@@ -1440,7 +1443,7 @@
       <c r="A63" s="7"/>
       <c r="B63" s="8"/>
       <c r="C63" s="9"/>
-      <c r="D63" s="15"/>
+      <c r="D63" s="16"/>
       <c r="E63" s="10"/>
       <c r="F63" s="10"/>
       <c r="G63" s="11"/>
@@ -1454,7 +1457,7 @@
       <c r="A64" s="7"/>
       <c r="B64" s="8"/>
       <c r="C64" s="9"/>
-      <c r="D64" s="15"/>
+      <c r="D64" s="16"/>
       <c r="E64" s="10"/>
       <c r="F64" s="10"/>
       <c r="G64" s="11"/>
@@ -1468,7 +1471,7 @@
       <c r="A65" s="7"/>
       <c r="B65" s="8"/>
       <c r="C65" s="9"/>
-      <c r="D65" s="15"/>
+      <c r="D65" s="16"/>
       <c r="E65" s="10"/>
       <c r="F65" s="10"/>
       <c r="G65" s="11"/>
@@ -1482,7 +1485,7 @@
       <c r="A66" s="7"/>
       <c r="B66" s="8"/>
       <c r="C66" s="9"/>
-      <c r="D66" s="15"/>
+      <c r="D66" s="16"/>
       <c r="E66" s="10"/>
       <c r="F66" s="10"/>
       <c r="G66" s="11"/>
@@ -1496,7 +1499,7 @@
       <c r="A67" s="7"/>
       <c r="B67" s="8"/>
       <c r="C67" s="9"/>
-      <c r="D67" s="15"/>
+      <c r="D67" s="16"/>
       <c r="E67" s="10"/>
       <c r="F67" s="10"/>
       <c r="G67" s="11"/>
@@ -1510,7 +1513,7 @@
       <c r="A68" s="7"/>
       <c r="B68" s="8"/>
       <c r="C68" s="9"/>
-      <c r="D68" s="15"/>
+      <c r="D68" s="16"/>
       <c r="E68" s="10"/>
       <c r="F68" s="10"/>
       <c r="G68" s="11"/>
@@ -1524,7 +1527,7 @@
       <c r="A69" s="7"/>
       <c r="B69" s="8"/>
       <c r="C69" s="9"/>
-      <c r="D69" s="15"/>
+      <c r="D69" s="16"/>
       <c r="E69" s="10"/>
       <c r="F69" s="10"/>
       <c r="G69" s="11"/>
@@ -1538,7 +1541,7 @@
       <c r="A70" s="7"/>
       <c r="B70" s="8"/>
       <c r="C70" s="9"/>
-      <c r="D70" s="15"/>
+      <c r="D70" s="16"/>
       <c r="E70" s="10"/>
       <c r="F70" s="10"/>
       <c r="G70" s="11"/>
@@ -1552,7 +1555,7 @@
       <c r="A71" s="7"/>
       <c r="B71" s="8"/>
       <c r="C71" s="9"/>
-      <c r="D71" s="15"/>
+      <c r="D71" s="16"/>
       <c r="E71" s="10"/>
       <c r="F71" s="10"/>
       <c r="G71" s="11"/>
@@ -1566,7 +1569,7 @@
       <c r="A72" s="7"/>
       <c r="B72" s="8"/>
       <c r="C72" s="9"/>
-      <c r="D72" s="15"/>
+      <c r="D72" s="16"/>
       <c r="E72" s="10"/>
       <c r="F72" s="10"/>
       <c r="G72" s="11"/>
@@ -1580,7 +1583,7 @@
       <c r="A73" s="7"/>
       <c r="B73" s="8"/>
       <c r="C73" s="9"/>
-      <c r="D73" s="15"/>
+      <c r="D73" s="16"/>
       <c r="E73" s="10"/>
       <c r="F73" s="10"/>
       <c r="G73" s="11"/>
@@ -1594,7 +1597,7 @@
       <c r="A74" s="7"/>
       <c r="B74" s="8"/>
       <c r="C74" s="9"/>
-      <c r="D74" s="15"/>
+      <c r="D74" s="16"/>
       <c r="E74" s="10"/>
       <c r="F74" s="10"/>
       <c r="G74" s="11"/>
@@ -1608,7 +1611,7 @@
       <c r="A75" s="7"/>
       <c r="B75" s="8"/>
       <c r="C75" s="9"/>
-      <c r="D75" s="15"/>
+      <c r="D75" s="16"/>
       <c r="E75" s="10"/>
       <c r="F75" s="10"/>
       <c r="G75" s="11"/>
@@ -1622,7 +1625,7 @@
       <c r="A76" s="7"/>
       <c r="B76" s="8"/>
       <c r="C76" s="9"/>
-      <c r="D76" s="15"/>
+      <c r="D76" s="16"/>
       <c r="E76" s="10"/>
       <c r="F76" s="10"/>
       <c r="G76" s="11"/>
@@ -1636,7 +1639,7 @@
       <c r="A77" s="7"/>
       <c r="B77" s="8"/>
       <c r="C77" s="9"/>
-      <c r="D77" s="15"/>
+      <c r="D77" s="16"/>
       <c r="E77" s="10"/>
       <c r="F77" s="10"/>
       <c r="G77" s="11"/>
@@ -1650,7 +1653,7 @@
       <c r="A78" s="7"/>
       <c r="B78" s="8"/>
       <c r="C78" s="9"/>
-      <c r="D78" s="15"/>
+      <c r="D78" s="16"/>
       <c r="E78" s="10"/>
       <c r="F78" s="10"/>
       <c r="G78" s="11"/>
@@ -1664,7 +1667,7 @@
       <c r="A79" s="7"/>
       <c r="B79" s="8"/>
       <c r="C79" s="9"/>
-      <c r="D79" s="15"/>
+      <c r="D79" s="16"/>
       <c r="E79" s="10"/>
       <c r="F79" s="10"/>
       <c r="G79" s="11"/>
@@ -1678,7 +1681,7 @@
       <c r="A80" s="7"/>
       <c r="B80" s="8"/>
       <c r="C80" s="9"/>
-      <c r="D80" s="15"/>
+      <c r="D80" s="16"/>
       <c r="E80" s="10"/>
       <c r="F80" s="10"/>
       <c r="G80" s="11"/>
@@ -1692,7 +1695,7 @@
       <c r="A81" s="7"/>
       <c r="B81" s="8"/>
       <c r="C81" s="9"/>
-      <c r="D81" s="15"/>
+      <c r="D81" s="16"/>
       <c r="E81" s="10"/>
       <c r="F81" s="10"/>
       <c r="G81" s="11"/>
@@ -1706,7 +1709,7 @@
       <c r="A82" s="7"/>
       <c r="B82" s="8"/>
       <c r="C82" s="9"/>
-      <c r="D82" s="15"/>
+      <c r="D82" s="16"/>
       <c r="E82" s="10"/>
       <c r="F82" s="10"/>
       <c r="G82" s="11"/>
@@ -1720,7 +1723,7 @@
       <c r="A83" s="7"/>
       <c r="B83" s="8"/>
       <c r="C83" s="9"/>
-      <c r="D83" s="15"/>
+      <c r="D83" s="16"/>
       <c r="E83" s="10"/>
       <c r="F83" s="10"/>
       <c r="G83" s="11"/>
@@ -1734,7 +1737,7 @@
       <c r="A84" s="7"/>
       <c r="B84" s="8"/>
       <c r="C84" s="9"/>
-      <c r="D84" s="15"/>
+      <c r="D84" s="16"/>
       <c r="E84" s="10"/>
       <c r="F84" s="10"/>
       <c r="G84" s="11"/>
@@ -1748,7 +1751,7 @@
       <c r="A85" s="7"/>
       <c r="B85" s="8"/>
       <c r="C85" s="9"/>
-      <c r="D85" s="15"/>
+      <c r="D85" s="16"/>
       <c r="E85" s="10"/>
       <c r="F85" s="10"/>
       <c r="G85" s="11"/>
@@ -1762,7 +1765,7 @@
       <c r="A86" s="7"/>
       <c r="B86" s="8"/>
       <c r="C86" s="9"/>
-      <c r="D86" s="15"/>
+      <c r="D86" s="16"/>
       <c r="E86" s="10"/>
       <c r="F86" s="10"/>
       <c r="G86" s="11"/>
@@ -1776,7 +1779,7 @@
       <c r="A87" s="7"/>
       <c r="B87" s="8"/>
       <c r="C87" s="9"/>
-      <c r="D87" s="15"/>
+      <c r="D87" s="16"/>
       <c r="E87" s="10"/>
       <c r="F87" s="10"/>
       <c r="G87" s="11"/>
@@ -1790,7 +1793,7 @@
       <c r="A88" s="7"/>
       <c r="B88" s="8"/>
       <c r="C88" s="9"/>
-      <c r="D88" s="15"/>
+      <c r="D88" s="16"/>
       <c r="E88" s="10"/>
       <c r="F88" s="10"/>
       <c r="G88" s="11"/>
@@ -1804,7 +1807,7 @@
       <c r="A89" s="7"/>
       <c r="B89" s="8"/>
       <c r="C89" s="9"/>
-      <c r="D89" s="15"/>
+      <c r="D89" s="16"/>
       <c r="E89" s="10"/>
       <c r="F89" s="10"/>
       <c r="G89" s="11"/>
@@ -1818,7 +1821,7 @@
       <c r="A90" s="7"/>
       <c r="B90" s="8"/>
       <c r="C90" s="9"/>
-      <c r="D90" s="15"/>
+      <c r="D90" s="16"/>
       <c r="E90" s="10"/>
       <c r="F90" s="10"/>
       <c r="G90" s="11"/>
@@ -1832,7 +1835,7 @@
       <c r="A91" s="7"/>
       <c r="B91" s="8"/>
       <c r="C91" s="9"/>
-      <c r="D91" s="15"/>
+      <c r="D91" s="16"/>
       <c r="E91" s="10"/>
       <c r="F91" s="10"/>
       <c r="G91" s="11"/>
@@ -1846,7 +1849,7 @@
       <c r="A92" s="7"/>
       <c r="B92" s="8"/>
       <c r="C92" s="9"/>
-      <c r="D92" s="15"/>
+      <c r="D92" s="16"/>
       <c r="E92" s="10"/>
       <c r="F92" s="10"/>
       <c r="G92" s="11"/>
@@ -1860,7 +1863,7 @@
       <c r="A93" s="7"/>
       <c r="B93" s="8"/>
       <c r="C93" s="9"/>
-      <c r="D93" s="15"/>
+      <c r="D93" s="16"/>
       <c r="E93" s="10"/>
       <c r="F93" s="10"/>
       <c r="G93" s="11"/>
@@ -1874,7 +1877,7 @@
       <c r="A94" s="7"/>
       <c r="B94" s="8"/>
       <c r="C94" s="9"/>
-      <c r="D94" s="15"/>
+      <c r="D94" s="16"/>
       <c r="E94" s="10"/>
       <c r="F94" s="10"/>
       <c r="G94" s="11"/>
@@ -1888,7 +1891,7 @@
       <c r="A95" s="7"/>
       <c r="B95" s="8"/>
       <c r="C95" s="9"/>
-      <c r="D95" s="15"/>
+      <c r="D95" s="16"/>
       <c r="E95" s="10"/>
       <c r="F95" s="10"/>
       <c r="G95" s="11"/>
@@ -1902,7 +1905,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="8"/>
       <c r="C96" s="9"/>
-      <c r="D96" s="15"/>
+      <c r="D96" s="16"/>
       <c r="E96" s="10"/>
       <c r="F96" s="10"/>
       <c r="G96" s="11"/>
@@ -1916,7 +1919,7 @@
       <c r="A97" s="7"/>
       <c r="B97" s="8"/>
       <c r="C97" s="9"/>
-      <c r="D97" s="15"/>
+      <c r="D97" s="16"/>
       <c r="E97" s="10"/>
       <c r="F97" s="10"/>
       <c r="G97" s="11"/>
@@ -1930,7 +1933,7 @@
       <c r="A98" s="7"/>
       <c r="B98" s="8"/>
       <c r="C98" s="9"/>
-      <c r="D98" s="15"/>
+      <c r="D98" s="16"/>
       <c r="E98" s="10"/>
       <c r="F98" s="10"/>
       <c r="G98" s="11"/>
@@ -1944,7 +1947,7 @@
       <c r="A99" s="7"/>
       <c r="B99" s="8"/>
       <c r="C99" s="9"/>
-      <c r="D99" s="15"/>
+      <c r="D99" s="16"/>
       <c r="E99" s="10"/>
       <c r="F99" s="10"/>
       <c r="G99" s="11"/>
@@ -1958,7 +1961,7 @@
       <c r="A100" s="7"/>
       <c r="B100" s="8"/>
       <c r="C100" s="9"/>
-      <c r="D100" s="15"/>
+      <c r="D100" s="16"/>
       <c r="E100" s="10"/>
       <c r="F100" s="10"/>
       <c r="G100" s="11"/>
@@ -1972,7 +1975,7 @@
       <c r="A101" s="7"/>
       <c r="B101" s="8"/>
       <c r="C101" s="9"/>
-      <c r="D101" s="15"/>
+      <c r="D101" s="16"/>
       <c r="E101" s="10"/>
       <c r="F101" s="10"/>
       <c r="G101" s="11"/>
@@ -1986,7 +1989,7 @@
       <c r="A102" s="7"/>
       <c r="B102" s="8"/>
       <c r="C102" s="9"/>
-      <c r="D102" s="15"/>
+      <c r="D102" s="16"/>
       <c r="E102" s="10"/>
       <c r="F102" s="10"/>
       <c r="G102" s="11"/>
@@ -2000,7 +2003,7 @@
       <c r="A103" s="7"/>
       <c r="B103" s="8"/>
       <c r="C103" s="9"/>
-      <c r="D103" s="15"/>
+      <c r="D103" s="16"/>
       <c r="E103" s="10"/>
       <c r="F103" s="10"/>
       <c r="G103" s="11"/>
@@ -2014,7 +2017,7 @@
       <c r="A104" s="7"/>
       <c r="B104" s="8"/>
       <c r="C104" s="9"/>
-      <c r="D104" s="15"/>
+      <c r="D104" s="16"/>
       <c r="E104" s="10"/>
       <c r="F104" s="10"/>
       <c r="G104" s="11"/>
@@ -2028,7 +2031,7 @@
       <c r="A105" s="7"/>
       <c r="B105" s="8"/>
       <c r="C105" s="9"/>
-      <c r="D105" s="15"/>
+      <c r="D105" s="16"/>
       <c r="E105" s="10"/>
       <c r="F105" s="10"/>
       <c r="G105" s="11"/>
@@ -2042,7 +2045,7 @@
       <c r="A106" s="7"/>
       <c r="B106" s="8"/>
       <c r="C106" s="9"/>
-      <c r="D106" s="15"/>
+      <c r="D106" s="16"/>
       <c r="E106" s="10"/>
       <c r="F106" s="10"/>
       <c r="G106" s="11"/>
@@ -2056,7 +2059,7 @@
       <c r="A107" s="7"/>
       <c r="B107" s="8"/>
       <c r="C107" s="9"/>
-      <c r="D107" s="15"/>
+      <c r="D107" s="16"/>
       <c r="E107" s="10"/>
       <c r="F107" s="10"/>
       <c r="G107" s="11"/>
@@ -2070,7 +2073,7 @@
       <c r="A108" s="7"/>
       <c r="B108" s="8"/>
       <c r="C108" s="9"/>
-      <c r="D108" s="15"/>
+      <c r="D108" s="16"/>
       <c r="E108" s="10"/>
       <c r="F108" s="10"/>
       <c r="G108" s="11"/>
@@ -2084,7 +2087,7 @@
       <c r="A109" s="7"/>
       <c r="B109" s="8"/>
       <c r="C109" s="9"/>
-      <c r="D109" s="15"/>
+      <c r="D109" s="16"/>
       <c r="E109" s="10"/>
       <c r="F109" s="10"/>
       <c r="G109" s="11"/>
@@ -2098,7 +2101,7 @@
       <c r="A110" s="7"/>
       <c r="B110" s="8"/>
       <c r="C110" s="9"/>
-      <c r="D110" s="15"/>
+      <c r="D110" s="16"/>
       <c r="E110" s="10"/>
       <c r="F110" s="10"/>
       <c r="G110" s="11"/>
@@ -2112,7 +2115,7 @@
       <c r="A111" s="7"/>
       <c r="B111" s="8"/>
       <c r="C111" s="9"/>
-      <c r="D111" s="15"/>
+      <c r="D111" s="16"/>
       <c r="E111" s="10"/>
       <c r="F111" s="10"/>
       <c r="G111" s="11"/>
@@ -2126,7 +2129,7 @@
       <c r="A112" s="7"/>
       <c r="B112" s="8"/>
       <c r="C112" s="9"/>
-      <c r="D112" s="15"/>
+      <c r="D112" s="16"/>
       <c r="E112" s="10"/>
       <c r="F112" s="10"/>
       <c r="G112" s="11"/>
@@ -2140,7 +2143,7 @@
       <c r="A113" s="7"/>
       <c r="B113" s="8"/>
       <c r="C113" s="9"/>
-      <c r="D113" s="15"/>
+      <c r="D113" s="16"/>
       <c r="E113" s="10"/>
       <c r="F113" s="10"/>
       <c r="G113" s="11"/>
@@ -2154,7 +2157,7 @@
       <c r="A114" s="7"/>
       <c r="B114" s="8"/>
       <c r="C114" s="9"/>
-      <c r="D114" s="15"/>
+      <c r="D114" s="16"/>
       <c r="E114" s="10"/>
       <c r="F114" s="10"/>
       <c r="G114" s="11"/>
@@ -2168,7 +2171,7 @@
       <c r="A115" s="7"/>
       <c r="B115" s="8"/>
       <c r="C115" s="9"/>
-      <c r="D115" s="15"/>
+      <c r="D115" s="16"/>
       <c r="E115" s="10"/>
       <c r="F115" s="10"/>
       <c r="G115" s="11"/>
@@ -2182,7 +2185,7 @@
       <c r="A116" s="7"/>
       <c r="B116" s="8"/>
       <c r="C116" s="9"/>
-      <c r="D116" s="15"/>
+      <c r="D116" s="16"/>
       <c r="E116" s="10"/>
       <c r="F116" s="10"/>
       <c r="G116" s="11"/>
@@ -2196,7 +2199,7 @@
       <c r="A117" s="7"/>
       <c r="B117" s="8"/>
       <c r="C117" s="9"/>
-      <c r="D117" s="15"/>
+      <c r="D117" s="16"/>
       <c r="E117" s="10"/>
       <c r="F117" s="10"/>
       <c r="G117" s="11"/>
@@ -2210,7 +2213,7 @@
       <c r="A118" s="7"/>
       <c r="B118" s="8"/>
       <c r="C118" s="9"/>
-      <c r="D118" s="15"/>
+      <c r="D118" s="16"/>
       <c r="E118" s="10"/>
       <c r="F118" s="10"/>
       <c r="G118" s="11"/>
@@ -2224,7 +2227,7 @@
       <c r="A119" s="7"/>
       <c r="B119" s="8"/>
       <c r="C119" s="9"/>
-      <c r="D119" s="15"/>
+      <c r="D119" s="16"/>
       <c r="E119" s="10"/>
       <c r="F119" s="10"/>
       <c r="G119" s="11"/>
@@ -2238,7 +2241,7 @@
       <c r="A120" s="7"/>
       <c r="B120" s="8"/>
       <c r="C120" s="9"/>
-      <c r="D120" s="15"/>
+      <c r="D120" s="16"/>
       <c r="E120" s="10"/>
       <c r="F120" s="10"/>
       <c r="G120" s="11"/>
@@ -2252,7 +2255,7 @@
       <c r="A121" s="7"/>
       <c r="B121" s="8"/>
       <c r="C121" s="9"/>
-      <c r="D121" s="15"/>
+      <c r="D121" s="16"/>
       <c r="E121" s="10"/>
       <c r="F121" s="10"/>
       <c r="G121" s="11"/>
@@ -2266,7 +2269,7 @@
       <c r="A122" s="7"/>
       <c r="B122" s="8"/>
       <c r="C122" s="9"/>
-      <c r="D122" s="15"/>
+      <c r="D122" s="16"/>
       <c r="E122" s="10"/>
       <c r="F122" s="10"/>
       <c r="G122" s="11"/>
@@ -2280,7 +2283,7 @@
       <c r="A123" s="7"/>
       <c r="B123" s="8"/>
       <c r="C123" s="9"/>
-      <c r="D123" s="15"/>
+      <c r="D123" s="16"/>
       <c r="E123" s="10"/>
       <c r="F123" s="10"/>
       <c r="G123" s="11"/>
@@ -2294,7 +2297,7 @@
       <c r="A124" s="7"/>
       <c r="B124" s="8"/>
       <c r="C124" s="9"/>
-      <c r="D124" s="15"/>
+      <c r="D124" s="16"/>
       <c r="E124" s="10"/>
       <c r="F124" s="10"/>
       <c r="G124" s="11"/>
@@ -2308,7 +2311,7 @@
       <c r="A125" s="7"/>
       <c r="B125" s="8"/>
       <c r="C125" s="9"/>
-      <c r="D125" s="15"/>
+      <c r="D125" s="16"/>
       <c r="E125" s="10"/>
       <c r="F125" s="10"/>
       <c r="G125" s="11"/>
@@ -2322,7 +2325,7 @@
       <c r="A126" s="7"/>
       <c r="B126" s="8"/>
       <c r="C126" s="9"/>
-      <c r="D126" s="15"/>
+      <c r="D126" s="16"/>
       <c r="E126" s="10"/>
       <c r="F126" s="10"/>
       <c r="G126" s="11"/>
@@ -2336,7 +2339,7 @@
       <c r="A127" s="7"/>
       <c r="B127" s="8"/>
       <c r="C127" s="9"/>
-      <c r="D127" s="15"/>
+      <c r="D127" s="16"/>
       <c r="E127" s="10"/>
       <c r="F127" s="10"/>
       <c r="G127" s="11"/>
@@ -2350,7 +2353,7 @@
       <c r="A128" s="7"/>
       <c r="B128" s="8"/>
       <c r="C128" s="9"/>
-      <c r="D128" s="15"/>
+      <c r="D128" s="16"/>
       <c r="E128" s="10"/>
       <c r="F128" s="10"/>
       <c r="G128" s="11"/>
@@ -2364,7 +2367,7 @@
       <c r="A129" s="7"/>
       <c r="B129" s="8"/>
       <c r="C129" s="9"/>
-      <c r="D129" s="15"/>
+      <c r="D129" s="16"/>
       <c r="E129" s="10"/>
       <c r="F129" s="10"/>
       <c r="G129" s="11"/>
@@ -2378,7 +2381,7 @@
       <c r="A130" s="7"/>
       <c r="B130" s="8"/>
       <c r="C130" s="9"/>
-      <c r="D130" s="15"/>
+      <c r="D130" s="16"/>
       <c r="E130" s="10"/>
       <c r="F130" s="10"/>
       <c r="G130" s="11"/>
@@ -2392,7 +2395,7 @@
       <c r="A131" s="7"/>
       <c r="B131" s="8"/>
       <c r="C131" s="9"/>
-      <c r="D131" s="15"/>
+      <c r="D131" s="16"/>
       <c r="E131" s="10"/>
       <c r="F131" s="10"/>
       <c r="G131" s="11"/>
@@ -2406,7 +2409,7 @@
       <c r="A132" s="7"/>
       <c r="B132" s="8"/>
       <c r="C132" s="9"/>
-      <c r="D132" s="15"/>
+      <c r="D132" s="16"/>
       <c r="E132" s="10"/>
       <c r="F132" s="10"/>
       <c r="G132" s="11"/>
@@ -2420,7 +2423,7 @@
       <c r="A133" s="7"/>
       <c r="B133" s="8"/>
       <c r="C133" s="9"/>
-      <c r="D133" s="15"/>
+      <c r="D133" s="16"/>
       <c r="E133" s="10"/>
       <c r="F133" s="10"/>
       <c r="G133" s="11"/>
@@ -2434,7 +2437,7 @@
       <c r="A134" s="7"/>
       <c r="B134" s="8"/>
       <c r="C134" s="9"/>
-      <c r="D134" s="15"/>
+      <c r="D134" s="16"/>
       <c r="E134" s="10"/>
       <c r="F134" s="10"/>
       <c r="G134" s="11"/>
@@ -2448,7 +2451,7 @@
       <c r="A135" s="7"/>
       <c r="B135" s="8"/>
       <c r="C135" s="9"/>
-      <c r="D135" s="15"/>
+      <c r="D135" s="16"/>
       <c r="E135" s="10"/>
       <c r="F135" s="10"/>
       <c r="G135" s="11"/>
@@ -2462,7 +2465,7 @@
       <c r="A136" s="7"/>
       <c r="B136" s="8"/>
       <c r="C136" s="9"/>
-      <c r="D136" s="15"/>
+      <c r="D136" s="16"/>
       <c r="E136" s="10"/>
       <c r="F136" s="10"/>
       <c r="G136" s="11"/>
@@ -2476,7 +2479,7 @@
       <c r="A137" s="7"/>
       <c r="B137" s="8"/>
       <c r="C137" s="9"/>
-      <c r="D137" s="15"/>
+      <c r="D137" s="16"/>
       <c r="E137" s="10"/>
       <c r="F137" s="10"/>
       <c r="G137" s="11"/>
@@ -2490,7 +2493,7 @@
       <c r="A138" s="7"/>
       <c r="B138" s="8"/>
       <c r="C138" s="9"/>
-      <c r="D138" s="15"/>
+      <c r="D138" s="16"/>
       <c r="E138" s="10"/>
       <c r="F138" s="10"/>
       <c r="G138" s="11"/>
@@ -2504,7 +2507,7 @@
       <c r="A139" s="7"/>
       <c r="B139" s="8"/>
       <c r="C139" s="9"/>
-      <c r="D139" s="15"/>
+      <c r="D139" s="16"/>
       <c r="E139" s="10"/>
       <c r="F139" s="10"/>
       <c r="G139" s="11"/>
@@ -2518,7 +2521,7 @@
       <c r="A140" s="7"/>
       <c r="B140" s="8"/>
       <c r="C140" s="9"/>
-      <c r="D140" s="15"/>
+      <c r="D140" s="16"/>
       <c r="E140" s="10"/>
       <c r="F140" s="10"/>
       <c r="G140" s="11"/>
@@ -2532,7 +2535,7 @@
       <c r="A141" s="7"/>
       <c r="B141" s="8"/>
       <c r="C141" s="9"/>
-      <c r="D141" s="15"/>
+      <c r="D141" s="16"/>
       <c r="E141" s="10"/>
       <c r="F141" s="10"/>
       <c r="G141" s="11"/>
@@ -2546,7 +2549,7 @@
       <c r="A142" s="7"/>
       <c r="B142" s="8"/>
       <c r="C142" s="9"/>
-      <c r="D142" s="15"/>
+      <c r="D142" s="16"/>
       <c r="E142" s="10"/>
       <c r="F142" s="10"/>
       <c r="G142" s="11"/>
@@ -2560,7 +2563,7 @@
       <c r="A143" s="7"/>
       <c r="B143" s="8"/>
       <c r="C143" s="9"/>
-      <c r="D143" s="15"/>
+      <c r="D143" s="16"/>
       <c r="E143" s="10"/>
       <c r="F143" s="10"/>
       <c r="G143" s="11"/>
@@ -2574,7 +2577,7 @@
       <c r="A144" s="7"/>
       <c r="B144" s="8"/>
       <c r="C144" s="9"/>
-      <c r="D144" s="15"/>
+      <c r="D144" s="16"/>
       <c r="E144" s="10"/>
       <c r="F144" s="10"/>
       <c r="G144" s="11"/>
@@ -2588,7 +2591,7 @@
       <c r="A145" s="7"/>
       <c r="B145" s="8"/>
       <c r="C145" s="9"/>
-      <c r="D145" s="15"/>
+      <c r="D145" s="16"/>
       <c r="E145" s="10"/>
       <c r="F145" s="10"/>
       <c r="G145" s="11"/>
@@ -2602,7 +2605,7 @@
       <c r="A146" s="7"/>
       <c r="B146" s="8"/>
       <c r="C146" s="9"/>
-      <c r="D146" s="15"/>
+      <c r="D146" s="16"/>
       <c r="E146" s="10"/>
       <c r="F146" s="10"/>
       <c r="G146" s="11"/>
@@ -2616,7 +2619,7 @@
       <c r="A147" s="7"/>
       <c r="B147" s="8"/>
       <c r="C147" s="9"/>
-      <c r="D147" s="15"/>
+      <c r="D147" s="16"/>
       <c r="E147" s="10"/>
       <c r="F147" s="10"/>
       <c r="G147" s="11"/>
@@ -2630,7 +2633,7 @@
       <c r="A148" s="7"/>
       <c r="B148" s="8"/>
       <c r="C148" s="9"/>
-      <c r="D148" s="15"/>
+      <c r="D148" s="16"/>
       <c r="E148" s="10"/>
       <c r="F148" s="10"/>
       <c r="G148" s="11"/>
@@ -2644,7 +2647,7 @@
       <c r="A149" s="7"/>
       <c r="B149" s="8"/>
       <c r="C149" s="9"/>
-      <c r="D149" s="15"/>
+      <c r="D149" s="16"/>
       <c r="E149" s="10"/>
       <c r="F149" s="10"/>
       <c r="G149" s="11"/>
@@ -2658,7 +2661,7 @@
       <c r="A150" s="7"/>
       <c r="B150" s="8"/>
       <c r="C150" s="9"/>
-      <c r="D150" s="15"/>
+      <c r="D150" s="16"/>
       <c r="E150" s="10"/>
       <c r="F150" s="10"/>
       <c r="G150" s="11"/>
@@ -2672,7 +2675,7 @@
       <c r="A151" s="7"/>
       <c r="B151" s="8"/>
       <c r="C151" s="9"/>
-      <c r="D151" s="15"/>
+      <c r="D151" s="16"/>
       <c r="E151" s="10"/>
       <c r="F151" s="10"/>
       <c r="G151" s="11"/>
@@ -2686,7 +2689,7 @@
       <c r="A152" s="7"/>
       <c r="B152" s="8"/>
       <c r="C152" s="9"/>
-      <c r="D152" s="15"/>
+      <c r="D152" s="16"/>
       <c r="E152" s="10"/>
       <c r="F152" s="10"/>
       <c r="G152" s="11"/>
@@ -2700,7 +2703,7 @@
       <c r="A153" s="7"/>
       <c r="B153" s="8"/>
       <c r="C153" s="9"/>
-      <c r="D153" s="15"/>
+      <c r="D153" s="16"/>
       <c r="E153" s="10"/>
       <c r="F153" s="10"/>
       <c r="G153" s="11"/>
@@ -2714,7 +2717,7 @@
       <c r="A154" s="7"/>
       <c r="B154" s="8"/>
       <c r="C154" s="9"/>
-      <c r="D154" s="15"/>
+      <c r="D154" s="16"/>
       <c r="E154" s="10"/>
       <c r="F154" s="10"/>
       <c r="G154" s="11"/>
@@ -2728,7 +2731,7 @@
       <c r="A155" s="7"/>
       <c r="B155" s="8"/>
       <c r="C155" s="9"/>
-      <c r="D155" s="15"/>
+      <c r="D155" s="16"/>
       <c r="E155" s="10"/>
       <c r="F155" s="10"/>
       <c r="G155" s="11"/>
@@ -2742,7 +2745,7 @@
       <c r="A156" s="7"/>
       <c r="B156" s="8"/>
       <c r="C156" s="9"/>
-      <c r="D156" s="15"/>
+      <c r="D156" s="16"/>
       <c r="E156" s="10"/>
       <c r="F156" s="10"/>
       <c r="G156" s="11"/>
@@ -2756,7 +2759,7 @@
       <c r="A157" s="7"/>
       <c r="B157" s="8"/>
       <c r="C157" s="9"/>
-      <c r="D157" s="15"/>
+      <c r="D157" s="16"/>
       <c r="E157" s="10"/>
       <c r="F157" s="10"/>
       <c r="G157" s="11"/>
@@ -2770,7 +2773,7 @@
       <c r="A158" s="7"/>
       <c r="B158" s="8"/>
       <c r="C158" s="9"/>
-      <c r="D158" s="15"/>
+      <c r="D158" s="16"/>
       <c r="E158" s="10"/>
       <c r="F158" s="10"/>
       <c r="G158" s="11"/>
@@ -2784,7 +2787,7 @@
       <c r="A159" s="7"/>
       <c r="B159" s="8"/>
       <c r="C159" s="9"/>
-      <c r="D159" s="15"/>
+      <c r="D159" s="16"/>
       <c r="E159" s="10"/>
       <c r="F159" s="10"/>
       <c r="G159" s="11"/>
@@ -2798,7 +2801,7 @@
       <c r="A160" s="7"/>
       <c r="B160" s="8"/>
       <c r="C160" s="9"/>
-      <c r="D160" s="15"/>
+      <c r="D160" s="16"/>
       <c r="E160" s="10"/>
       <c r="F160" s="10"/>
       <c r="G160" s="11"/>
@@ -2812,7 +2815,7 @@
       <c r="A161" s="7"/>
       <c r="B161" s="8"/>
       <c r="C161" s="9"/>
-      <c r="D161" s="15"/>
+      <c r="D161" s="16"/>
       <c r="E161" s="10"/>
       <c r="F161" s="10"/>
       <c r="G161" s="11"/>
@@ -2826,7 +2829,7 @@
       <c r="A162" s="7"/>
       <c r="B162" s="8"/>
       <c r="C162" s="9"/>
-      <c r="D162" s="15"/>
+      <c r="D162" s="16"/>
       <c r="E162" s="10"/>
       <c r="F162" s="10"/>
       <c r="G162" s="11"/>
@@ -2840,7 +2843,7 @@
       <c r="A163" s="7"/>
       <c r="B163" s="8"/>
       <c r="C163" s="9"/>
-      <c r="D163" s="15"/>
+      <c r="D163" s="16"/>
       <c r="E163" s="10"/>
       <c r="F163" s="10"/>
       <c r="G163" s="11"/>
@@ -2854,7 +2857,7 @@
       <c r="A164" s="7"/>
       <c r="B164" s="8"/>
       <c r="C164" s="9"/>
-      <c r="D164" s="15"/>
+      <c r="D164" s="16"/>
       <c r="E164" s="10"/>
       <c r="F164" s="10"/>
       <c r="G164" s="11"/>
@@ -2868,7 +2871,7 @@
       <c r="A165" s="7"/>
       <c r="B165" s="8"/>
       <c r="C165" s="9"/>
-      <c r="D165" s="15"/>
+      <c r="D165" s="16"/>
       <c r="E165" s="10"/>
       <c r="F165" s="10"/>
       <c r="G165" s="11"/>
@@ -2882,7 +2885,7 @@
       <c r="A166" s="7"/>
       <c r="B166" s="8"/>
       <c r="C166" s="9"/>
-      <c r="D166" s="15"/>
+      <c r="D166" s="16"/>
       <c r="E166" s="10"/>
       <c r="F166" s="10"/>
       <c r="G166" s="11"/>
@@ -2896,7 +2899,7 @@
       <c r="A167" s="7"/>
       <c r="B167" s="8"/>
       <c r="C167" s="9"/>
-      <c r="D167" s="15"/>
+      <c r="D167" s="16"/>
       <c r="E167" s="10"/>
       <c r="F167" s="10"/>
       <c r="G167" s="11"/>
@@ -2910,7 +2913,7 @@
       <c r="A168" s="7"/>
       <c r="B168" s="8"/>
       <c r="C168" s="9"/>
-      <c r="D168" s="15"/>
+      <c r="D168" s="16"/>
       <c r="E168" s="10"/>
       <c r="F168" s="10"/>
       <c r="G168" s="11"/>
@@ -2924,7 +2927,7 @@
       <c r="A169" s="7"/>
       <c r="B169" s="8"/>
       <c r="C169" s="9"/>
-      <c r="D169" s="15"/>
+      <c r="D169" s="16"/>
       <c r="E169" s="10"/>
       <c r="F169" s="10"/>
       <c r="G169" s="11"/>
@@ -2938,7 +2941,7 @@
       <c r="A170" s="7"/>
       <c r="B170" s="8"/>
       <c r="C170" s="9"/>
-      <c r="D170" s="15"/>
+      <c r="D170" s="16"/>
       <c r="E170" s="10"/>
       <c r="F170" s="10"/>
       <c r="G170" s="11"/>
@@ -2952,7 +2955,7 @@
       <c r="A171" s="7"/>
       <c r="B171" s="8"/>
       <c r="C171" s="9"/>
-      <c r="D171" s="15"/>
+      <c r="D171" s="16"/>
       <c r="E171" s="10"/>
       <c r="F171" s="10"/>
       <c r="G171" s="11"/>
@@ -2966,7 +2969,7 @@
       <c r="A172" s="7"/>
       <c r="B172" s="8"/>
       <c r="C172" s="9"/>
-      <c r="D172" s="15"/>
+      <c r="D172" s="16"/>
       <c r="E172" s="10"/>
       <c r="F172" s="10"/>
       <c r="G172" s="11"/>
@@ -2980,7 +2983,7 @@
       <c r="A173" s="7"/>
       <c r="B173" s="8"/>
       <c r="C173" s="9"/>
-      <c r="D173" s="15"/>
+      <c r="D173" s="16"/>
       <c r="E173" s="10"/>
       <c r="F173" s="10"/>
       <c r="G173" s="11"/>
@@ -2994,7 +2997,7 @@
       <c r="A174" s="7"/>
       <c r="B174" s="8"/>
       <c r="C174" s="9"/>
-      <c r="D174" s="15"/>
+      <c r="D174" s="16"/>
       <c r="E174" s="10"/>
       <c r="F174" s="10"/>
       <c r="G174" s="11"/>
@@ -3008,7 +3011,7 @@
       <c r="A175" s="7"/>
       <c r="B175" s="8"/>
       <c r="C175" s="9"/>
-      <c r="D175" s="15"/>
+      <c r="D175" s="16"/>
       <c r="E175" s="10"/>
       <c r="F175" s="10"/>
       <c r="G175" s="11"/>
@@ -3022,7 +3025,7 @@
       <c r="A176" s="7"/>
       <c r="B176" s="8"/>
       <c r="C176" s="9"/>
-      <c r="D176" s="15"/>
+      <c r="D176" s="16"/>
       <c r="E176" s="10"/>
       <c r="F176" s="10"/>
       <c r="G176" s="11"/>
@@ -3036,7 +3039,7 @@
       <c r="A177" s="7"/>
       <c r="B177" s="8"/>
       <c r="C177" s="9"/>
-      <c r="D177" s="15"/>
+      <c r="D177" s="16"/>
       <c r="E177" s="10"/>
       <c r="F177" s="10"/>
       <c r="G177" s="11"/>
@@ -3050,7 +3053,7 @@
       <c r="A178" s="7"/>
       <c r="B178" s="8"/>
       <c r="C178" s="9"/>
-      <c r="D178" s="15"/>
+      <c r="D178" s="16"/>
       <c r="E178" s="10"/>
       <c r="F178" s="10"/>
       <c r="G178" s="11"/>
@@ -3064,7 +3067,7 @@
       <c r="A179" s="7"/>
       <c r="B179" s="8"/>
       <c r="C179" s="9"/>
-      <c r="D179" s="15"/>
+      <c r="D179" s="16"/>
       <c r="E179" s="10"/>
       <c r="F179" s="10"/>
       <c r="G179" s="11"/>
@@ -3078,7 +3081,7 @@
       <c r="A180" s="7"/>
       <c r="B180" s="8"/>
       <c r="C180" s="9"/>
-      <c r="D180" s="15"/>
+      <c r="D180" s="16"/>
       <c r="E180" s="10"/>
       <c r="F180" s="10"/>
       <c r="G180" s="11"/>
@@ -3092,7 +3095,7 @@
       <c r="A181" s="7"/>
       <c r="B181" s="8"/>
       <c r="C181" s="9"/>
-      <c r="D181" s="15"/>
+      <c r="D181" s="16"/>
       <c r="E181" s="10"/>
       <c r="F181" s="10"/>
       <c r="G181" s="11"/>
@@ -3106,7 +3109,7 @@
       <c r="A182" s="7"/>
       <c r="B182" s="8"/>
       <c r="C182" s="9"/>
-      <c r="D182" s="15"/>
+      <c r="D182" s="16"/>
       <c r="E182" s="10"/>
       <c r="F182" s="10"/>
       <c r="G182" s="11"/>
@@ -3120,7 +3123,7 @@
       <c r="A183" s="7"/>
       <c r="B183" s="8"/>
       <c r="C183" s="9"/>
-      <c r="D183" s="15"/>
+      <c r="D183" s="16"/>
       <c r="E183" s="10"/>
       <c r="F183" s="10"/>
       <c r="G183" s="11"/>
@@ -3134,7 +3137,7 @@
       <c r="A184" s="7"/>
       <c r="B184" s="8"/>
       <c r="C184" s="9"/>
-      <c r="D184" s="15"/>
+      <c r="D184" s="16"/>
       <c r="E184" s="10"/>
       <c r="F184" s="10"/>
       <c r="G184" s="11"/>
@@ -3148,7 +3151,7 @@
       <c r="A185" s="7"/>
       <c r="B185" s="8"/>
       <c r="C185" s="9"/>
-      <c r="D185" s="15"/>
+      <c r="D185" s="16"/>
       <c r="E185" s="10"/>
       <c r="F185" s="10"/>
       <c r="G185" s="11"/>
@@ -3162,7 +3165,7 @@
       <c r="A186" s="7"/>
       <c r="B186" s="8"/>
       <c r="C186" s="9"/>
-      <c r="D186" s="15"/>
+      <c r="D186" s="16"/>
       <c r="E186" s="10"/>
       <c r="F186" s="10"/>
       <c r="G186" s="11"/>
@@ -3176,7 +3179,7 @@
       <c r="A187" s="7"/>
       <c r="B187" s="8"/>
       <c r="C187" s="9"/>
-      <c r="D187" s="15"/>
+      <c r="D187" s="16"/>
       <c r="E187" s="10"/>
       <c r="F187" s="10"/>
       <c r="G187" s="11"/>
@@ -3190,7 +3193,7 @@
       <c r="A188" s="7"/>
       <c r="B188" s="8"/>
       <c r="C188" s="9"/>
-      <c r="D188" s="15"/>
+      <c r="D188" s="16"/>
       <c r="E188" s="10"/>
       <c r="F188" s="10"/>
       <c r="G188" s="11"/>
@@ -3204,7 +3207,7 @@
       <c r="A189" s="7"/>
       <c r="B189" s="8"/>
       <c r="C189" s="9"/>
-      <c r="D189" s="15"/>
+      <c r="D189" s="16"/>
       <c r="E189" s="10"/>
       <c r="F189" s="10"/>
       <c r="G189" s="11"/>
@@ -3218,7 +3221,7 @@
       <c r="A190" s="7"/>
       <c r="B190" s="8"/>
       <c r="C190" s="9"/>
-      <c r="D190" s="15"/>
+      <c r="D190" s="16"/>
       <c r="E190" s="10"/>
       <c r="F190" s="10"/>
       <c r="G190" s="11"/>
@@ -3232,7 +3235,7 @@
       <c r="A191" s="7"/>
       <c r="B191" s="8"/>
       <c r="C191" s="9"/>
-      <c r="D191" s="15"/>
+      <c r="D191" s="16"/>
       <c r="E191" s="10"/>
       <c r="F191" s="10"/>
       <c r="G191" s="11"/>
@@ -3246,7 +3249,7 @@
       <c r="A192" s="7"/>
       <c r="B192" s="8"/>
       <c r="C192" s="9"/>
-      <c r="D192" s="15"/>
+      <c r="D192" s="16"/>
       <c r="E192" s="10"/>
       <c r="F192" s="10"/>
       <c r="G192" s="11"/>
@@ -3260,7 +3263,7 @@
       <c r="A193" s="7"/>
       <c r="B193" s="8"/>
       <c r="C193" s="9"/>
-      <c r="D193" s="15"/>
+      <c r="D193" s="16"/>
       <c r="E193" s="10"/>
       <c r="F193" s="10"/>
       <c r="G193" s="11"/>
@@ -3274,7 +3277,7 @@
       <c r="A194" s="7"/>
       <c r="B194" s="8"/>
       <c r="C194" s="9"/>
-      <c r="D194" s="15"/>
+      <c r="D194" s="16"/>
       <c r="E194" s="10"/>
       <c r="F194" s="10"/>
       <c r="G194" s="11"/>
@@ -3288,7 +3291,7 @@
       <c r="A195" s="7"/>
       <c r="B195" s="8"/>
       <c r="C195" s="9"/>
-      <c r="D195" s="15"/>
+      <c r="D195" s="16"/>
       <c r="E195" s="10"/>
       <c r="F195" s="10"/>
       <c r="G195" s="11"/>
@@ -3302,7 +3305,7 @@
       <c r="A196" s="7"/>
       <c r="B196" s="8"/>
       <c r="C196" s="9"/>
-      <c r="D196" s="15"/>
+      <c r="D196" s="16"/>
       <c r="E196" s="10"/>
       <c r="F196" s="10"/>
       <c r="G196" s="11"/>
@@ -3316,7 +3319,7 @@
       <c r="A197" s="7"/>
       <c r="B197" s="8"/>
       <c r="C197" s="9"/>
-      <c r="D197" s="15"/>
+      <c r="D197" s="16"/>
       <c r="E197" s="10"/>
       <c r="F197" s="10"/>
       <c r="G197" s="11"/>
@@ -3330,7 +3333,7 @@
       <c r="A198" s="7"/>
       <c r="B198" s="8"/>
       <c r="C198" s="9"/>
-      <c r="D198" s="15"/>
+      <c r="D198" s="16"/>
       <c r="E198" s="10"/>
       <c r="F198" s="10"/>
       <c r="G198" s="11"/>
@@ -3344,7 +3347,7 @@
       <c r="A199" s="7"/>
       <c r="B199" s="8"/>
       <c r="C199" s="9"/>
-      <c r="D199" s="15"/>
+      <c r="D199" s="16"/>
       <c r="E199" s="10"/>
       <c r="F199" s="10"/>
       <c r="G199" s="11"/>
@@ -3358,7 +3361,7 @@
       <c r="A200" s="7"/>
       <c r="B200" s="8"/>
       <c r="C200" s="9"/>
-      <c r="D200" s="15"/>
+      <c r="D200" s="16"/>
       <c r="E200" s="10"/>
       <c r="F200" s="10"/>
       <c r="G200" s="11"/>
@@ -3372,7 +3375,7 @@
       <c r="A201" s="7"/>
       <c r="B201" s="8"/>
       <c r="C201" s="9"/>
-      <c r="D201" s="15"/>
+      <c r="D201" s="16"/>
       <c r="E201" s="10"/>
       <c r="F201" s="10"/>
       <c r="G201" s="11"/>
@@ -3386,7 +3389,7 @@
       <c r="A202" s="7"/>
       <c r="B202" s="8"/>
       <c r="C202" s="9"/>
-      <c r="D202" s="15"/>
+      <c r="D202" s="16"/>
       <c r="E202" s="10"/>
       <c r="F202" s="10"/>
       <c r="G202" s="11"/>
@@ -3400,7 +3403,7 @@
       <c r="A203" s="7"/>
       <c r="B203" s="8"/>
       <c r="C203" s="9"/>
-      <c r="D203" s="15"/>
+      <c r="D203" s="16"/>
       <c r="E203" s="10"/>
       <c r="F203" s="10"/>
       <c r="G203" s="11"/>
@@ -3414,7 +3417,7 @@
       <c r="A204" s="7"/>
       <c r="B204" s="8"/>
       <c r="C204" s="9"/>
-      <c r="D204" s="15"/>
+      <c r="D204" s="16"/>
       <c r="E204" s="10"/>
       <c r="F204" s="10"/>
       <c r="G204" s="11"/>
@@ -3428,7 +3431,7 @@
       <c r="A205" s="7"/>
       <c r="B205" s="8"/>
       <c r="C205" s="9"/>
-      <c r="D205" s="15"/>
+      <c r="D205" s="16"/>
       <c r="E205" s="10"/>
       <c r="F205" s="10"/>
       <c r="G205" s="11"/>
@@ -3442,7 +3445,7 @@
       <c r="A206" s="7"/>
       <c r="B206" s="8"/>
       <c r="C206" s="9"/>
-      <c r="D206" s="15"/>
+      <c r="D206" s="16"/>
       <c r="E206" s="10"/>
       <c r="F206" s="10"/>
       <c r="G206" s="11"/>
@@ -3456,7 +3459,7 @@
       <c r="A207" s="7"/>
       <c r="B207" s="8"/>
       <c r="C207" s="9"/>
-      <c r="D207" s="15"/>
+      <c r="D207" s="16"/>
       <c r="E207" s="10"/>
       <c r="F207" s="10"/>
       <c r="G207" s="11"/>
@@ -3470,7 +3473,7 @@
       <c r="A208" s="7"/>
       <c r="B208" s="8"/>
       <c r="C208" s="9"/>
-      <c r="D208" s="15"/>
+      <c r="D208" s="16"/>
       <c r="E208" s="10"/>
       <c r="F208" s="10"/>
       <c r="G208" s="11"/>
@@ -3484,7 +3487,7 @@
       <c r="A209" s="7"/>
       <c r="B209" s="8"/>
       <c r="C209" s="9"/>
-      <c r="D209" s="15"/>
+      <c r="D209" s="16"/>
       <c r="E209" s="10"/>
       <c r="F209" s="10"/>
       <c r="G209" s="11"/>
@@ -3498,7 +3501,7 @@
       <c r="A210" s="7"/>
       <c r="B210" s="8"/>
       <c r="C210" s="9"/>
-      <c r="D210" s="15"/>
+      <c r="D210" s="16"/>
       <c r="E210" s="10"/>
       <c r="F210" s="10"/>
       <c r="G210" s="11"/>
@@ -3512,7 +3515,7 @@
       <c r="A211" s="7"/>
       <c r="B211" s="8"/>
       <c r="C211" s="9"/>
-      <c r="D211" s="15"/>
+      <c r="D211" s="16"/>
       <c r="E211" s="10"/>
       <c r="F211" s="10"/>
       <c r="G211" s="11"/>
@@ -3526,7 +3529,7 @@
       <c r="A212" s="7"/>
       <c r="B212" s="8"/>
       <c r="C212" s="9"/>
-      <c r="D212" s="15"/>
+      <c r="D212" s="16"/>
       <c r="E212" s="10"/>
       <c r="F212" s="10"/>
       <c r="G212" s="11"/>
@@ -3540,7 +3543,7 @@
       <c r="A213" s="7"/>
       <c r="B213" s="8"/>
       <c r="C213" s="9"/>
-      <c r="D213" s="15"/>
+      <c r="D213" s="16"/>
       <c r="E213" s="10"/>
       <c r="F213" s="10"/>
       <c r="G213" s="11"/>
@@ -3554,7 +3557,7 @@
       <c r="A214" s="7"/>
       <c r="B214" s="8"/>
       <c r="C214" s="9"/>
-      <c r="D214" s="15"/>
+      <c r="D214" s="16"/>
       <c r="E214" s="10"/>
       <c r="F214" s="10"/>
       <c r="G214" s="11"/>
@@ -3568,7 +3571,7 @@
       <c r="A215" s="7"/>
       <c r="B215" s="8"/>
       <c r="C215" s="9"/>
-      <c r="D215" s="15"/>
+      <c r="D215" s="16"/>
       <c r="E215" s="10"/>
       <c r="F215" s="10"/>
       <c r="G215" s="11"/>
@@ -3582,7 +3585,7 @@
       <c r="A216" s="7"/>
       <c r="B216" s="8"/>
       <c r="C216" s="9"/>
-      <c r="D216" s="15"/>
+      <c r="D216" s="16"/>
       <c r="E216" s="10"/>
       <c r="F216" s="10"/>
       <c r="G216" s="11"/>
@@ -3596,7 +3599,7 @@
       <c r="A217" s="7"/>
       <c r="B217" s="8"/>
       <c r="C217" s="9"/>
-      <c r="D217" s="15"/>
+      <c r="D217" s="16"/>
       <c r="E217" s="10"/>
       <c r="F217" s="10"/>
       <c r="G217" s="11"/>
@@ -3610,7 +3613,7 @@
       <c r="A218" s="7"/>
       <c r="B218" s="8"/>
       <c r="C218" s="9"/>
-      <c r="D218" s="15"/>
+      <c r="D218" s="16"/>
       <c r="E218" s="10"/>
       <c r="F218" s="10"/>
       <c r="G218" s="11"/>
@@ -3624,7 +3627,7 @@
       <c r="A219" s="7"/>
       <c r="B219" s="8"/>
       <c r="C219" s="9"/>
-      <c r="D219" s="15"/>
+      <c r="D219" s="16"/>
       <c r="E219" s="10"/>
       <c r="F219" s="10"/>
       <c r="G219" s="11"/>
@@ -3638,7 +3641,7 @@
       <c r="A220" s="7"/>
       <c r="B220" s="8"/>
       <c r="C220" s="9"/>
-      <c r="D220" s="15"/>
+      <c r="D220" s="16"/>
       <c r="E220" s="10"/>
       <c r="F220" s="10"/>
       <c r="G220" s="11"/>
@@ -3652,7 +3655,7 @@
       <c r="A221" s="7"/>
       <c r="B221" s="8"/>
       <c r="C221" s="9"/>
-      <c r="D221" s="15"/>
+      <c r="D221" s="16"/>
       <c r="E221" s="10"/>
       <c r="F221" s="10"/>
       <c r="G221" s="11"/>
@@ -3666,7 +3669,7 @@
       <c r="A222" s="7"/>
       <c r="B222" s="8"/>
       <c r="C222" s="9"/>
-      <c r="D222" s="15"/>
+      <c r="D222" s="16"/>
       <c r="E222" s="10"/>
       <c r="F222" s="10"/>
       <c r="G222" s="11"/>
@@ -3680,7 +3683,7 @@
       <c r="A223" s="7"/>
       <c r="B223" s="8"/>
       <c r="C223" s="9"/>
-      <c r="D223" s="15"/>
+      <c r="D223" s="16"/>
       <c r="E223" s="10"/>
       <c r="F223" s="10"/>
       <c r="G223" s="11"/>
@@ -3694,7 +3697,7 @@
       <c r="A224" s="7"/>
       <c r="B224" s="8"/>
       <c r="C224" s="9"/>
-      <c r="D224" s="15"/>
+      <c r="D224" s="16"/>
       <c r="E224" s="10"/>
       <c r="F224" s="10"/>
       <c r="G224" s="11"/>
@@ -3708,7 +3711,7 @@
       <c r="A225" s="7"/>
       <c r="B225" s="8"/>
       <c r="C225" s="9"/>
-      <c r="D225" s="15"/>
+      <c r="D225" s="16"/>
       <c r="E225" s="10"/>
       <c r="F225" s="10"/>
       <c r="G225" s="11"/>
@@ -3722,7 +3725,7 @@
       <c r="A226" s="7"/>
       <c r="B226" s="8"/>
       <c r="C226" s="9"/>
-      <c r="D226" s="15"/>
+      <c r="D226" s="16"/>
       <c r="E226" s="10"/>
       <c r="F226" s="10"/>
       <c r="G226" s="11"/>
@@ -3736,7 +3739,7 @@
       <c r="A227" s="7"/>
       <c r="B227" s="8"/>
       <c r="C227" s="9"/>
-      <c r="D227" s="15"/>
+      <c r="D227" s="16"/>
       <c r="E227" s="10"/>
       <c r="F227" s="10"/>
       <c r="G227" s="11"/>
@@ -3750,7 +3753,7 @@
       <c r="A228" s="7"/>
       <c r="B228" s="8"/>
       <c r="C228" s="9"/>
-      <c r="D228" s="15"/>
+      <c r="D228" s="16"/>
       <c r="E228" s="10"/>
       <c r="F228" s="10"/>
       <c r="G228" s="11"/>
@@ -3764,7 +3767,7 @@
       <c r="A229" s="7"/>
       <c r="B229" s="8"/>
       <c r="C229" s="9"/>
-      <c r="D229" s="15"/>
+      <c r="D229" s="16"/>
       <c r="E229" s="10"/>
       <c r="F229" s="10"/>
       <c r="G229" s="11"/>
@@ -3778,7 +3781,7 @@
       <c r="A230" s="7"/>
       <c r="B230" s="8"/>
       <c r="C230" s="9"/>
-      <c r="D230" s="15"/>
+      <c r="D230" s="16"/>
       <c r="E230" s="10"/>
       <c r="F230" s="10"/>
       <c r="G230" s="11"/>
@@ -3792,7 +3795,7 @@
       <c r="A231" s="7"/>
       <c r="B231" s="8"/>
       <c r="C231" s="9"/>
-      <c r="D231" s="15"/>
+      <c r="D231" s="16"/>
       <c r="E231" s="10"/>
       <c r="F231" s="10"/>
       <c r="G231" s="11"/>
@@ -3806,7 +3809,7 @@
       <c r="A232" s="7"/>
       <c r="B232" s="8"/>
       <c r="C232" s="9"/>
-      <c r="D232" s="15"/>
+      <c r="D232" s="16"/>
       <c r="E232" s="10"/>
       <c r="F232" s="10"/>
       <c r="G232" s="11"/>
@@ -3820,7 +3823,7 @@
       <c r="A233" s="7"/>
       <c r="B233" s="8"/>
       <c r="C233" s="9"/>
-      <c r="D233" s="15"/>
+      <c r="D233" s="16"/>
       <c r="E233" s="10"/>
       <c r="F233" s="10"/>
       <c r="G233" s="11"/>
@@ -3834,7 +3837,7 @@
       <c r="A234" s="7"/>
       <c r="B234" s="8"/>
       <c r="C234" s="9"/>
-      <c r="D234" s="15"/>
+      <c r="D234" s="16"/>
       <c r="E234" s="10"/>
       <c r="F234" s="10"/>
       <c r="G234" s="11"/>
@@ -3848,7 +3851,7 @@
       <c r="A235" s="7"/>
       <c r="B235" s="8"/>
       <c r="C235" s="9"/>
-      <c r="D235" s="15"/>
+      <c r="D235" s="16"/>
       <c r="E235" s="10"/>
       <c r="F235" s="10"/>
       <c r="G235" s="11"/>
@@ -3862,7 +3865,7 @@
       <c r="A236" s="7"/>
       <c r="B236" s="8"/>
       <c r="C236" s="9"/>
-      <c r="D236" s="15"/>
+      <c r="D236" s="16"/>
       <c r="E236" s="10"/>
       <c r="F236" s="10"/>
       <c r="G236" s="11"/>
@@ -3876,7 +3879,7 @@
       <c r="A237" s="7"/>
       <c r="B237" s="8"/>
       <c r="C237" s="9"/>
-      <c r="D237" s="15"/>
+      <c r="D237" s="16"/>
       <c r="E237" s="10"/>
       <c r="F237" s="10"/>
       <c r="G237" s="11"/>
@@ -3890,7 +3893,7 @@
       <c r="A238" s="7"/>
       <c r="B238" s="8"/>
       <c r="C238" s="9"/>
-      <c r="D238" s="15"/>
+      <c r="D238" s="16"/>
       <c r="E238" s="10"/>
       <c r="F238" s="10"/>
       <c r="G238" s="11"/>
@@ -3904,7 +3907,7 @@
       <c r="A239" s="7"/>
       <c r="B239" s="8"/>
       <c r="C239" s="9"/>
-      <c r="D239" s="15"/>
+      <c r="D239" s="16"/>
       <c r="E239" s="10"/>
       <c r="F239" s="10"/>
       <c r="G239" s="11"/>
@@ -3918,7 +3921,7 @@
       <c r="A240" s="7"/>
       <c r="B240" s="8"/>
       <c r="C240" s="9"/>
-      <c r="D240" s="15"/>
+      <c r="D240" s="16"/>
       <c r="E240" s="10"/>
       <c r="F240" s="10"/>
       <c r="G240" s="11"/>
@@ -3932,7 +3935,7 @@
       <c r="A241" s="7"/>
       <c r="B241" s="8"/>
       <c r="C241" s="9"/>
-      <c r="D241" s="15"/>
+      <c r="D241" s="16"/>
       <c r="E241" s="10"/>
       <c r="F241" s="10"/>
       <c r="G241" s="11"/>
@@ -3946,7 +3949,7 @@
       <c r="A242" s="7"/>
       <c r="B242" s="8"/>
       <c r="C242" s="9"/>
-      <c r="D242" s="15"/>
+      <c r="D242" s="16"/>
       <c r="E242" s="10"/>
       <c r="F242" s="10"/>
       <c r="G242" s="11"/>
@@ -3960,7 +3963,7 @@
       <c r="A243" s="7"/>
       <c r="B243" s="8"/>
       <c r="C243" s="9"/>
-      <c r="D243" s="15"/>
+      <c r="D243" s="16"/>
       <c r="E243" s="10"/>
       <c r="F243" s="10"/>
       <c r="G243" s="11"/>
@@ -3974,7 +3977,7 @@
       <c r="A244" s="7"/>
       <c r="B244" s="8"/>
       <c r="C244" s="9"/>
-      <c r="D244" s="15"/>
+      <c r="D244" s="16"/>
       <c r="E244" s="10"/>
       <c r="F244" s="10"/>
       <c r="G244" s="11"/>
@@ -3988,7 +3991,7 @@
       <c r="A245" s="7"/>
       <c r="B245" s="8"/>
       <c r="C245" s="9"/>
-      <c r="D245" s="15"/>
+      <c r="D245" s="16"/>
       <c r="E245" s="10"/>
       <c r="F245" s="10"/>
       <c r="G245" s="11"/>
@@ -4002,7 +4005,7 @@
       <c r="A246" s="7"/>
       <c r="B246" s="8"/>
       <c r="C246" s="9"/>
-      <c r="D246" s="15"/>
+      <c r="D246" s="16"/>
       <c r="E246" s="10"/>
       <c r="F246" s="10"/>
       <c r="G246" s="11"/>
@@ -4016,7 +4019,7 @@
       <c r="A247" s="7"/>
       <c r="B247" s="8"/>
       <c r="C247" s="9"/>
-      <c r="D247" s="15"/>
+      <c r="D247" s="16"/>
       <c r="E247" s="10"/>
       <c r="F247" s="10"/>
       <c r="G247" s="11"/>
@@ -4030,7 +4033,7 @@
       <c r="A248" s="7"/>
       <c r="B248" s="8"/>
       <c r="C248" s="9"/>
-      <c r="D248" s="15"/>
+      <c r="D248" s="16"/>
       <c r="E248" s="10"/>
       <c r="F248" s="10"/>
       <c r="G248" s="11"/>
@@ -4044,7 +4047,7 @@
       <c r="A249" s="7"/>
       <c r="B249" s="8"/>
       <c r="C249" s="9"/>
-      <c r="D249" s="15"/>
+      <c r="D249" s="16"/>
       <c r="E249" s="10"/>
       <c r="F249" s="10"/>
       <c r="G249" s="11"/>
@@ -4058,7 +4061,7 @@
       <c r="A250" s="7"/>
       <c r="B250" s="8"/>
       <c r="C250" s="9"/>
-      <c r="D250" s="15"/>
+      <c r="D250" s="16"/>
       <c r="E250" s="10"/>
       <c r="F250" s="10"/>
       <c r="G250" s="11"/>
@@ -4072,7 +4075,7 @@
       <c r="A251" s="7"/>
       <c r="B251" s="8"/>
       <c r="C251" s="9"/>
-      <c r="D251" s="15"/>
+      <c r="D251" s="16"/>
       <c r="E251" s="10"/>
       <c r="F251" s="10"/>
       <c r="G251" s="11"/>
@@ -4086,7 +4089,7 @@
       <c r="A252" s="7"/>
       <c r="B252" s="8"/>
       <c r="C252" s="9"/>
-      <c r="D252" s="15"/>
+      <c r="D252" s="16"/>
       <c r="E252" s="10"/>
       <c r="F252" s="10"/>
       <c r="G252" s="11"/>
@@ -4100,7 +4103,7 @@
       <c r="A253" s="7"/>
       <c r="B253" s="8"/>
       <c r="C253" s="9"/>
-      <c r="D253" s="15"/>
+      <c r="D253" s="16"/>
       <c r="E253" s="10"/>
       <c r="F253" s="10"/>
       <c r="G253" s="11"/>
@@ -4114,7 +4117,7 @@
       <c r="A254" s="7"/>
       <c r="B254" s="8"/>
       <c r="C254" s="9"/>
-      <c r="D254" s="15"/>
+      <c r="D254" s="16"/>
       <c r="E254" s="10"/>
       <c r="F254" s="10"/>
       <c r="G254" s="11"/>
@@ -4128,7 +4131,7 @@
       <c r="A255" s="7"/>
       <c r="B255" s="8"/>
       <c r="C255" s="9"/>
-      <c r="D255" s="15"/>
+      <c r="D255" s="16"/>
       <c r="E255" s="10"/>
       <c r="F255" s="10"/>
       <c r="G255" s="11"/>
@@ -4142,7 +4145,7 @@
       <c r="A256" s="7"/>
       <c r="B256" s="8"/>
       <c r="C256" s="9"/>
-      <c r="D256" s="15"/>
+      <c r="D256" s="16"/>
       <c r="E256" s="10"/>
       <c r="F256" s="10"/>
       <c r="G256" s="11"/>
@@ -4156,7 +4159,7 @@
       <c r="A257" s="7"/>
       <c r="B257" s="8"/>
       <c r="C257" s="9"/>
-      <c r="D257" s="15"/>
+      <c r="D257" s="16"/>
       <c r="E257" s="10"/>
       <c r="F257" s="10"/>
       <c r="G257" s="11"/>
@@ -4170,7 +4173,7 @@
       <c r="A258" s="7"/>
       <c r="B258" s="8"/>
       <c r="C258" s="9"/>
-      <c r="D258" s="15"/>
+      <c r="D258" s="16"/>
       <c r="E258" s="10"/>
       <c r="F258" s="10"/>
       <c r="G258" s="11"/>
@@ -4184,7 +4187,7 @@
       <c r="A259" s="7"/>
       <c r="B259" s="8"/>
       <c r="C259" s="9"/>
-      <c r="D259" s="15"/>
+      <c r="D259" s="16"/>
       <c r="E259" s="10"/>
       <c r="F259" s="10"/>
       <c r="G259" s="11"/>
@@ -4198,7 +4201,7 @@
       <c r="A260" s="7"/>
       <c r="B260" s="8"/>
       <c r="C260" s="9"/>
-      <c r="D260" s="15"/>
+      <c r="D260" s="16"/>
       <c r="E260" s="10"/>
       <c r="F260" s="10"/>
       <c r="G260" s="11"/>
@@ -4212,7 +4215,7 @@
       <c r="A261" s="7"/>
       <c r="B261" s="8"/>
       <c r="C261" s="9"/>
-      <c r="D261" s="15"/>
+      <c r="D261" s="16"/>
       <c r="E261" s="10"/>
       <c r="F261" s="10"/>
       <c r="G261" s="11"/>
@@ -4226,7 +4229,7 @@
       <c r="A262" s="7"/>
       <c r="B262" s="8"/>
       <c r="C262" s="9"/>
-      <c r="D262" s="15"/>
+      <c r="D262" s="16"/>
       <c r="E262" s="10"/>
       <c r="F262" s="10"/>
       <c r="G262" s="11"/>
@@ -4240,7 +4243,7 @@
       <c r="A263" s="7"/>
       <c r="B263" s="8"/>
       <c r="C263" s="9"/>
-      <c r="D263" s="15"/>
+      <c r="D263" s="16"/>
       <c r="E263" s="10"/>
       <c r="F263" s="10"/>
       <c r="G263" s="11"/>
@@ -4254,7 +4257,7 @@
       <c r="A264" s="7"/>
       <c r="B264" s="8"/>
       <c r="C264" s="9"/>
-      <c r="D264" s="15"/>
+      <c r="D264" s="16"/>
       <c r="E264" s="10"/>
       <c r="F264" s="10"/>
       <c r="G264" s="11"/>
@@ -4268,7 +4271,7 @@
       <c r="A265" s="7"/>
       <c r="B265" s="8"/>
       <c r="C265" s="9"/>
-      <c r="D265" s="15"/>
+      <c r="D265" s="16"/>
       <c r="E265" s="10"/>
       <c r="F265" s="10"/>
       <c r="G265" s="11"/>
@@ -4282,7 +4285,7 @@
       <c r="A266" s="7"/>
       <c r="B266" s="8"/>
       <c r="C266" s="9"/>
-      <c r="D266" s="15"/>
+      <c r="D266" s="16"/>
       <c r="E266" s="10"/>
       <c r="F266" s="10"/>
       <c r="G266" s="11"/>
@@ -4296,7 +4299,7 @@
       <c r="A267" s="7"/>
       <c r="B267" s="8"/>
       <c r="C267" s="9"/>
-      <c r="D267" s="15"/>
+      <c r="D267" s="16"/>
       <c r="E267" s="10"/>
       <c r="F267" s="10"/>
       <c r="G267" s="11"/>
@@ -4310,7 +4313,7 @@
       <c r="A268" s="7"/>
       <c r="B268" s="8"/>
       <c r="C268" s="9"/>
-      <c r="D268" s="15"/>
+      <c r="D268" s="16"/>
       <c r="E268" s="10"/>
       <c r="F268" s="10"/>
       <c r="G268" s="11"/>
@@ -4324,7 +4327,7 @@
       <c r="A269" s="7"/>
       <c r="B269" s="8"/>
       <c r="C269" s="9"/>
-      <c r="D269" s="15"/>
+      <c r="D269" s="16"/>
       <c r="E269" s="10"/>
       <c r="F269" s="10"/>
       <c r="G269" s="11"/>
@@ -4338,7 +4341,7 @@
       <c r="A270" s="7"/>
       <c r="B270" s="8"/>
       <c r="C270" s="9"/>
-      <c r="D270" s="15"/>
+      <c r="D270" s="16"/>
       <c r="E270" s="10"/>
       <c r="F270" s="10"/>
       <c r="G270" s="11"/>
@@ -4352,7 +4355,7 @@
       <c r="A271" s="7"/>
       <c r="B271" s="8"/>
       <c r="C271" s="9"/>
-      <c r="D271" s="15"/>
+      <c r="D271" s="16"/>
       <c r="E271" s="10"/>
       <c r="F271" s="10"/>
       <c r="G271" s="11"/>
@@ -4366,7 +4369,7 @@
       <c r="A272" s="7"/>
       <c r="B272" s="8"/>
       <c r="C272" s="9"/>
-      <c r="D272" s="15"/>
+      <c r="D272" s="16"/>
       <c r="E272" s="10"/>
       <c r="F272" s="10"/>
       <c r="G272" s="11"/>
@@ -4380,7 +4383,7 @@
       <c r="A273" s="7"/>
       <c r="B273" s="8"/>
       <c r="C273" s="9"/>
-      <c r="D273" s="15"/>
+      <c r="D273" s="16"/>
       <c r="E273" s="10"/>
       <c r="F273" s="10"/>
       <c r="G273" s="11"/>
@@ -4394,7 +4397,7 @@
       <c r="A274" s="7"/>
       <c r="B274" s="8"/>
       <c r="C274" s="9"/>
-      <c r="D274" s="15"/>
+      <c r="D274" s="16"/>
       <c r="E274" s="10"/>
       <c r="F274" s="10"/>
       <c r="G274" s="11"/>
@@ -4408,7 +4411,7 @@
       <c r="A275" s="7"/>
       <c r="B275" s="8"/>
       <c r="C275" s="9"/>
-      <c r="D275" s="15"/>
+      <c r="D275" s="16"/>
       <c r="E275" s="10"/>
       <c r="F275" s="10"/>
       <c r="G275" s="11"/>
@@ -4422,7 +4425,7 @@
       <c r="A276" s="7"/>
       <c r="B276" s="8"/>
       <c r="C276" s="9"/>
-      <c r="D276" s="15"/>
+      <c r="D276" s="16"/>
       <c r="E276" s="10"/>
       <c r="F276" s="10"/>
       <c r="G276" s="11"/>
@@ -4436,7 +4439,7 @@
       <c r="A277" s="7"/>
       <c r="B277" s="8"/>
       <c r="C277" s="9"/>
-      <c r="D277" s="15"/>
+      <c r="D277" s="16"/>
       <c r="E277" s="10"/>
       <c r="F277" s="10"/>
       <c r="G277" s="11"/>
@@ -4450,7 +4453,7 @@
       <c r="A278" s="7"/>
       <c r="B278" s="8"/>
       <c r="C278" s="9"/>
-      <c r="D278" s="15"/>
+      <c r="D278" s="16"/>
       <c r="E278" s="10"/>
       <c r="F278" s="10"/>
       <c r="G278" s="11"/>
@@ -4464,7 +4467,7 @@
       <c r="A279" s="7"/>
       <c r="B279" s="8"/>
       <c r="C279" s="9"/>
-      <c r="D279" s="15"/>
+      <c r="D279" s="16"/>
       <c r="E279" s="10"/>
       <c r="F279" s="10"/>
       <c r="G279" s="11"/>
@@ -4478,7 +4481,7 @@
       <c r="A280" s="7"/>
       <c r="B280" s="8"/>
       <c r="C280" s="9"/>
-      <c r="D280" s="15"/>
+      <c r="D280" s="16"/>
       <c r="E280" s="10"/>
       <c r="F280" s="10"/>
       <c r="G280" s="11"/>
@@ -4492,7 +4495,7 @@
       <c r="A281" s="7"/>
       <c r="B281" s="8"/>
       <c r="C281" s="9"/>
-      <c r="D281" s="15"/>
+      <c r="D281" s="16"/>
       <c r="E281" s="10"/>
       <c r="F281" s="10"/>
       <c r="G281" s="11"/>
@@ -4506,7 +4509,7 @@
       <c r="A282" s="7"/>
       <c r="B282" s="8"/>
       <c r="C282" s="9"/>
-      <c r="D282" s="15"/>
+      <c r="D282" s="16"/>
       <c r="E282" s="10"/>
       <c r="F282" s="10"/>
       <c r="G282" s="11"/>
@@ -4520,7 +4523,7 @@
       <c r="A283" s="7"/>
       <c r="B283" s="8"/>
       <c r="C283" s="9"/>
-      <c r="D283" s="15"/>
+      <c r="D283" s="16"/>
       <c r="E283" s="10"/>
       <c r="F283" s="10"/>
       <c r="G283" s="11"/>
@@ -4534,7 +4537,7 @@
       <c r="A284" s="7"/>
       <c r="B284" s="8"/>
       <c r="C284" s="9"/>
-      <c r="D284" s="15"/>
+      <c r="D284" s="16"/>
       <c r="E284" s="10"/>
       <c r="F284" s="10"/>
       <c r="G284" s="11"/>
@@ -4548,7 +4551,7 @@
       <c r="A285" s="7"/>
       <c r="B285" s="8"/>
       <c r="C285" s="9"/>
-      <c r="D285" s="15"/>
+      <c r="D285" s="16"/>
       <c r="E285" s="10"/>
       <c r="F285" s="10"/>
       <c r="G285" s="11"/>
@@ -4562,7 +4565,7 @@
       <c r="A286" s="7"/>
       <c r="B286" s="8"/>
       <c r="C286" s="9"/>
-      <c r="D286" s="15"/>
+      <c r="D286" s="16"/>
       <c r="E286" s="10"/>
       <c r="F286" s="10"/>
       <c r="G286" s="11"/>
@@ -4576,7 +4579,7 @@
       <c r="A287" s="7"/>
       <c r="B287" s="8"/>
       <c r="C287" s="9"/>
-      <c r="D287" s="15"/>
+      <c r="D287" s="16"/>
       <c r="E287" s="10"/>
       <c r="F287" s="10"/>
       <c r="G287" s="11"/>
@@ -4590,7 +4593,7 @@
       <c r="A288" s="7"/>
       <c r="B288" s="8"/>
       <c r="C288" s="9"/>
-      <c r="D288" s="15"/>
+      <c r="D288" s="16"/>
       <c r="E288" s="10"/>
       <c r="F288" s="10"/>
       <c r="G288" s="11"/>
@@ -4604,7 +4607,7 @@
       <c r="A289" s="7"/>
       <c r="B289" s="8"/>
       <c r="C289" s="9"/>
-      <c r="D289" s="15"/>
+      <c r="D289" s="16"/>
       <c r="E289" s="10"/>
       <c r="F289" s="10"/>
       <c r="G289" s="11"/>
@@ -4618,7 +4621,7 @@
       <c r="A290" s="7"/>
       <c r="B290" s="8"/>
       <c r="C290" s="9"/>
-      <c r="D290" s="15"/>
+      <c r="D290" s="16"/>
       <c r="E290" s="10"/>
       <c r="F290" s="10"/>
       <c r="G290" s="11"/>
@@ -4632,7 +4635,7 @@
       <c r="A291" s="7"/>
       <c r="B291" s="8"/>
       <c r="C291" s="9"/>
-      <c r="D291" s="15"/>
+      <c r="D291" s="16"/>
       <c r="E291" s="10"/>
       <c r="F291" s="10"/>
       <c r="G291" s="11"/>
@@ -4646,7 +4649,7 @@
       <c r="A292" s="7"/>
       <c r="B292" s="8"/>
       <c r="C292" s="9"/>
-      <c r="D292" s="15"/>
+      <c r="D292" s="16"/>
       <c r="E292" s="10"/>
       <c r="F292" s="10"/>
       <c r="G292" s="11"/>
@@ -4660,7 +4663,7 @@
       <c r="A293" s="7"/>
       <c r="B293" s="8"/>
       <c r="C293" s="9"/>
-      <c r="D293" s="15"/>
+      <c r="D293" s="16"/>
       <c r="E293" s="10"/>
       <c r="F293" s="10"/>
       <c r="G293" s="11"/>
@@ -4674,7 +4677,7 @@
       <c r="A294" s="7"/>
       <c r="B294" s="8"/>
       <c r="C294" s="9"/>
-      <c r="D294" s="15"/>
+      <c r="D294" s="16"/>
       <c r="E294" s="10"/>
       <c r="F294" s="10"/>
       <c r="G294" s="11"/>
@@ -4688,7 +4691,7 @@
       <c r="A295" s="7"/>
       <c r="B295" s="8"/>
       <c r="C295" s="9"/>
-      <c r="D295" s="15"/>
+      <c r="D295" s="16"/>
       <c r="E295" s="10"/>
       <c r="F295" s="10"/>
       <c r="G295" s="11"/>
@@ -4702,7 +4705,7 @@
       <c r="A296" s="7"/>
       <c r="B296" s="8"/>
       <c r="C296" s="9"/>
-      <c r="D296" s="15"/>
+      <c r="D296" s="16"/>
       <c r="E296" s="10"/>
       <c r="F296" s="10"/>
       <c r="G296" s="11"/>
@@ -4716,7 +4719,7 @@
       <c r="A297" s="7"/>
       <c r="B297" s="8"/>
       <c r="C297" s="9"/>
-      <c r="D297" s="15"/>
+      <c r="D297" s="16"/>
       <c r="E297" s="10"/>
       <c r="F297" s="10"/>
       <c r="G297" s="11"/>
@@ -4730,7 +4733,7 @@
       <c r="A298" s="7"/>
       <c r="B298" s="8"/>
       <c r="C298" s="9"/>
-      <c r="D298" s="15"/>
+      <c r="D298" s="16"/>
       <c r="E298" s="10"/>
       <c r="F298" s="10"/>
       <c r="G298" s="11"/>
@@ -4744,7 +4747,7 @@
       <c r="A299" s="7"/>
       <c r="B299" s="8"/>
       <c r="C299" s="9"/>
-      <c r="D299" s="15"/>
+      <c r="D299" s="16"/>
       <c r="E299" s="10"/>
       <c r="F299" s="10"/>
       <c r="G299" s="11"/>
@@ -4758,7 +4761,7 @@
       <c r="A300" s="7"/>
       <c r="B300" s="8"/>
       <c r="C300" s="9"/>
-      <c r="D300" s="15"/>
+      <c r="D300" s="16"/>
       <c r="E300" s="10"/>
       <c r="F300" s="10"/>
       <c r="G300" s="11"/>
@@ -4772,7 +4775,7 @@
       <c r="A301" s="7"/>
       <c r="B301" s="8"/>
       <c r="C301" s="9"/>
-      <c r="D301" s="15"/>
+      <c r="D301" s="16"/>
       <c r="E301" s="10"/>
       <c r="F301" s="10"/>
       <c r="G301" s="11"/>
@@ -4786,7 +4789,7 @@
       <c r="A302" s="7"/>
       <c r="B302" s="8"/>
       <c r="C302" s="9"/>
-      <c r="D302" s="15"/>
+      <c r="D302" s="16"/>
       <c r="E302" s="10"/>
       <c r="F302" s="10"/>
       <c r="G302" s="11"/>
@@ -4800,7 +4803,7 @@
       <c r="A303" s="7"/>
       <c r="B303" s="8"/>
       <c r="C303" s="9"/>
-      <c r="D303" s="15"/>
+      <c r="D303" s="16"/>
       <c r="E303" s="10"/>
       <c r="F303" s="10"/>
       <c r="G303" s="11"/>
@@ -4814,7 +4817,7 @@
       <c r="A304" s="7"/>
       <c r="B304" s="8"/>
       <c r="C304" s="9"/>
-      <c r="D304" s="15"/>
+      <c r="D304" s="16"/>
       <c r="E304" s="10"/>
       <c r="F304" s="10"/>
       <c r="G304" s="11"/>
@@ -4828,7 +4831,7 @@
       <c r="A305" s="7"/>
       <c r="B305" s="8"/>
       <c r="C305" s="9"/>
-      <c r="D305" s="15"/>
+      <c r="D305" s="16"/>
       <c r="E305" s="10"/>
       <c r="F305" s="10"/>
       <c r="G305" s="11"/>
@@ -4842,7 +4845,7 @@
       <c r="A306" s="7"/>
       <c r="B306" s="8"/>
       <c r="C306" s="9"/>
-      <c r="D306" s="15"/>
+      <c r="D306" s="16"/>
       <c r="E306" s="10"/>
       <c r="F306" s="10"/>
       <c r="G306" s="11"/>
@@ -4856,7 +4859,7 @@
       <c r="A307" s="7"/>
       <c r="B307" s="8"/>
       <c r="C307" s="9"/>
-      <c r="D307" s="15"/>
+      <c r="D307" s="16"/>
       <c r="E307" s="10"/>
       <c r="F307" s="10"/>
       <c r="G307" s="11"/>
@@ -4870,7 +4873,7 @@
       <c r="A308" s="7"/>
       <c r="B308" s="8"/>
       <c r="C308" s="9"/>
-      <c r="D308" s="15"/>
+      <c r="D308" s="16"/>
       <c r="E308" s="10"/>
       <c r="F308" s="10"/>
       <c r="G308" s="11"/>
@@ -4884,7 +4887,7 @@
       <c r="A309" s="7"/>
       <c r="B309" s="8"/>
       <c r="C309" s="9"/>
-      <c r="D309" s="15"/>
+      <c r="D309" s="16"/>
       <c r="E309" s="10"/>
       <c r="F309" s="10"/>
       <c r="G309" s="11"/>
@@ -4898,7 +4901,7 @@
       <c r="A310" s="7"/>
       <c r="B310" s="8"/>
       <c r="C310" s="9"/>
-      <c r="D310" s="15"/>
+      <c r="D310" s="16"/>
       <c r="E310" s="10"/>
       <c r="F310" s="10"/>
       <c r="G310" s="11"/>
@@ -4912,7 +4915,7 @@
       <c r="A311" s="7"/>
       <c r="B311" s="8"/>
       <c r="C311" s="9"/>
-      <c r="D311" s="15"/>
+      <c r="D311" s="16"/>
       <c r="E311" s="10"/>
       <c r="F311" s="10"/>
       <c r="G311" s="11"/>
@@ -4926,7 +4929,7 @@
       <c r="A312" s="7"/>
       <c r="B312" s="8"/>
       <c r="C312" s="9"/>
-      <c r="D312" s="15"/>
+      <c r="D312" s="16"/>
       <c r="E312" s="10"/>
       <c r="F312" s="10"/>
       <c r="G312" s="11"/>
@@ -4940,7 +4943,7 @@
       <c r="A313" s="7"/>
       <c r="B313" s="8"/>
       <c r="C313" s="9"/>
-      <c r="D313" s="15"/>
+      <c r="D313" s="16"/>
       <c r="E313" s="10"/>
       <c r="F313" s="10"/>
       <c r="G313" s="11"/>
@@ -4954,7 +4957,7 @@
       <c r="A314" s="7"/>
       <c r="B314" s="8"/>
       <c r="C314" s="9"/>
-      <c r="D314" s="15"/>
+      <c r="D314" s="16"/>
       <c r="E314" s="10"/>
       <c r="F314" s="10"/>
       <c r="G314" s="11"/>
@@ -4968,7 +4971,7 @@
       <c r="A315" s="7"/>
       <c r="B315" s="8"/>
       <c r="C315" s="9"/>
-      <c r="D315" s="15"/>
+      <c r="D315" s="16"/>
       <c r="E315" s="10"/>
       <c r="F315" s="10"/>
       <c r="G315" s="11"/>
@@ -4982,7 +4985,7 @@
       <c r="A316" s="7"/>
       <c r="B316" s="8"/>
       <c r="C316" s="9"/>
-      <c r="D316" s="15"/>
+      <c r="D316" s="16"/>
       <c r="E316" s="10"/>
       <c r="F316" s="10"/>
       <c r="G316" s="11"/>
@@ -4996,7 +4999,7 @@
       <c r="A317" s="7"/>
       <c r="B317" s="8"/>
       <c r="C317" s="9"/>
-      <c r="D317" s="15"/>
+      <c r="D317" s="16"/>
       <c r="E317" s="10"/>
       <c r="F317" s="10"/>
       <c r="G317" s="11"/>
@@ -5010,7 +5013,7 @@
       <c r="A318" s="7"/>
       <c r="B318" s="8"/>
       <c r="C318" s="9"/>
-      <c r="D318" s="15"/>
+      <c r="D318" s="16"/>
       <c r="E318" s="10"/>
       <c r="F318" s="10"/>
       <c r="G318" s="11"/>
@@ -5024,7 +5027,7 @@
       <c r="A319" s="7"/>
       <c r="B319" s="8"/>
       <c r="C319" s="9"/>
-      <c r="D319" s="15"/>
+      <c r="D319" s="16"/>
       <c r="E319" s="10"/>
       <c r="F319" s="10"/>
       <c r="G319" s="11"/>
@@ -5038,7 +5041,7 @@
       <c r="A320" s="7"/>
       <c r="B320" s="8"/>
       <c r="C320" s="9"/>
-      <c r="D320" s="15"/>
+      <c r="D320" s="16"/>
       <c r="E320" s="10"/>
       <c r="F320" s="10"/>
       <c r="G320" s="11"/>
@@ -5052,7 +5055,7 @@
       <c r="A321" s="7"/>
       <c r="B321" s="8"/>
       <c r="C321" s="9"/>
-      <c r="D321" s="15"/>
+      <c r="D321" s="16"/>
       <c r="E321" s="10"/>
       <c r="F321" s="10"/>
       <c r="G321" s="11"/>
@@ -5066,7 +5069,7 @@
       <c r="A322" s="7"/>
       <c r="B322" s="8"/>
       <c r="C322" s="9"/>
-      <c r="D322" s="15"/>
+      <c r="D322" s="16"/>
       <c r="E322" s="10"/>
       <c r="F322" s="10"/>
       <c r="G322" s="11"/>
@@ -5080,7 +5083,7 @@
       <c r="A323" s="7"/>
       <c r="B323" s="8"/>
       <c r="C323" s="9"/>
-      <c r="D323" s="15"/>
+      <c r="D323" s="16"/>
       <c r="E323" s="10"/>
       <c r="F323" s="10"/>
       <c r="G323" s="11"/>
@@ -5094,7 +5097,7 @@
       <c r="A324" s="7"/>
       <c r="B324" s="8"/>
       <c r="C324" s="9"/>
-      <c r="D324" s="15"/>
+      <c r="D324" s="16"/>
       <c r="E324" s="10"/>
       <c r="F324" s="10"/>
       <c r="G324" s="11"/>
@@ -5108,7 +5111,7 @@
       <c r="A325" s="7"/>
       <c r="B325" s="8"/>
       <c r="C325" s="9"/>
-      <c r="D325" s="15"/>
+      <c r="D325" s="16"/>
       <c r="E325" s="10"/>
       <c r="F325" s="10"/>
       <c r="G325" s="11"/>
@@ -5122,7 +5125,7 @@
       <c r="A326" s="7"/>
       <c r="B326" s="8"/>
       <c r="C326" s="9"/>
-      <c r="D326" s="15"/>
+      <c r="D326" s="16"/>
       <c r="E326" s="10"/>
       <c r="F326" s="10"/>
       <c r="G326" s="11"/>
@@ -5136,7 +5139,7 @@
       <c r="A327" s="7"/>
       <c r="B327" s="8"/>
       <c r="C327" s="9"/>
-      <c r="D327" s="15"/>
+      <c r="D327" s="16"/>
       <c r="E327" s="10"/>
       <c r="F327" s="10"/>
       <c r="G327" s="11"/>
@@ -5150,7 +5153,7 @@
       <c r="A328" s="7"/>
       <c r="B328" s="8"/>
       <c r="C328" s="9"/>
-      <c r="D328" s="15"/>
+      <c r="D328" s="16"/>
       <c r="E328" s="10"/>
       <c r="F328" s="10"/>
       <c r="G328" s="11"/>
@@ -5164,7 +5167,7 @@
       <c r="A329" s="7"/>
       <c r="B329" s="8"/>
       <c r="C329" s="9"/>
-      <c r="D329" s="15"/>
+      <c r="D329" s="16"/>
       <c r="E329" s="10"/>
       <c r="F329" s="10"/>
       <c r="G329" s="11"/>
@@ -5178,7 +5181,7 @@
       <c r="A330" s="7"/>
       <c r="B330" s="8"/>
       <c r="C330" s="9"/>
-      <c r="D330" s="15"/>
+      <c r="D330" s="16"/>
       <c r="E330" s="10"/>
       <c r="F330" s="10"/>
       <c r="G330" s="11"/>
@@ -5192,7 +5195,7 @@
       <c r="A331" s="7"/>
       <c r="B331" s="8"/>
       <c r="C331" s="9"/>
-      <c r="D331" s="15"/>
+      <c r="D331" s="16"/>
       <c r="E331" s="10"/>
       <c r="F331" s="10"/>
       <c r="G331" s="11"/>
@@ -5206,7 +5209,7 @@
       <c r="A332" s="7"/>
       <c r="B332" s="8"/>
       <c r="C332" s="9"/>
-      <c r="D332" s="15"/>
+      <c r="D332" s="16"/>
       <c r="E332" s="10"/>
       <c r="F332" s="10"/>
       <c r="G332" s="11"/>
@@ -5220,7 +5223,7 @@
       <c r="A333" s="7"/>
       <c r="B333" s="8"/>
       <c r="C333" s="9"/>
-      <c r="D333" s="15"/>
+      <c r="D333" s="16"/>
       <c r="E333" s="10"/>
       <c r="F333" s="10"/>
       <c r="G333" s="11"/>
@@ -5234,7 +5237,7 @@
       <c r="A334" s="7"/>
       <c r="B334" s="8"/>
       <c r="C334" s="9"/>
-      <c r="D334" s="15"/>
+      <c r="D334" s="16"/>
       <c r="E334" s="10"/>
       <c r="F334" s="10"/>
       <c r="G334" s="11"/>
@@ -5248,7 +5251,7 @@
       <c r="A335" s="7"/>
       <c r="B335" s="8"/>
       <c r="C335" s="9"/>
-      <c r="D335" s="15"/>
+      <c r="D335" s="16"/>
       <c r="E335" s="10"/>
       <c r="F335" s="10"/>
       <c r="G335" s="11"/>
@@ -5262,7 +5265,7 @@
       <c r="A336" s="7"/>
       <c r="B336" s="8"/>
       <c r="C336" s="9"/>
-      <c r="D336" s="15"/>
+      <c r="D336" s="16"/>
       <c r="E336" s="10"/>
       <c r="F336" s="10"/>
       <c r="G336" s="11"/>
@@ -5276,7 +5279,7 @@
       <c r="A337" s="7"/>
       <c r="B337" s="8"/>
       <c r="C337" s="9"/>
-      <c r="D337" s="15"/>
+      <c r="D337" s="16"/>
       <c r="E337" s="10"/>
       <c r="F337" s="10"/>
       <c r="G337" s="11"/>
@@ -5290,7 +5293,7 @@
       <c r="A338" s="7"/>
       <c r="B338" s="8"/>
       <c r="C338" s="9"/>
-      <c r="D338" s="15"/>
+      <c r="D338" s="16"/>
       <c r="E338" s="10"/>
       <c r="F338" s="10"/>
       <c r="G338" s="11"/>
@@ -5304,7 +5307,7 @@
       <c r="A339" s="7"/>
       <c r="B339" s="8"/>
       <c r="C339" s="9"/>
-      <c r="D339" s="15"/>
+      <c r="D339" s="16"/>
       <c r="E339" s="10"/>
       <c r="F339" s="10"/>
       <c r="G339" s="11"/>
@@ -5318,7 +5321,7 @@
       <c r="A340" s="7"/>
       <c r="B340" s="8"/>
       <c r="C340" s="9"/>
-      <c r="D340" s="15"/>
+      <c r="D340" s="16"/>
       <c r="E340" s="10"/>
       <c r="F340" s="10"/>
       <c r="G340" s="11"/>
@@ -5332,7 +5335,7 @@
       <c r="A341" s="7"/>
       <c r="B341" s="8"/>
       <c r="C341" s="9"/>
-      <c r="D341" s="15"/>
+      <c r="D341" s="16"/>
       <c r="E341" s="10"/>
       <c r="F341" s="10"/>
       <c r="G341" s="11"/>
@@ -5346,7 +5349,7 @@
       <c r="A342" s="7"/>
       <c r="B342" s="8"/>
       <c r="C342" s="9"/>
-      <c r="D342" s="15"/>
+      <c r="D342" s="16"/>
       <c r="E342" s="10"/>
       <c r="F342" s="10"/>
       <c r="G342" s="11"/>
@@ -5360,7 +5363,7 @@
       <c r="A343" s="7"/>
       <c r="B343" s="8"/>
       <c r="C343" s="9"/>
-      <c r="D343" s="15"/>
+      <c r="D343" s="16"/>
       <c r="E343" s="10"/>
       <c r="F343" s="10"/>
       <c r="G343" s="11"/>
@@ -5374,7 +5377,7 @@
       <c r="A344" s="7"/>
       <c r="B344" s="8"/>
       <c r="C344" s="9"/>
-      <c r="D344" s="15"/>
+      <c r="D344" s="16"/>
       <c r="E344" s="10"/>
       <c r="F344" s="10"/>
       <c r="G344" s="11"/>
@@ -5388,7 +5391,7 @@
       <c r="A345" s="7"/>
       <c r="B345" s="8"/>
       <c r="C345" s="9"/>
-      <c r="D345" s="15"/>
+      <c r="D345" s="16"/>
       <c r="E345" s="10"/>
       <c r="F345" s="10"/>
       <c r="G345" s="11"/>
@@ -5402,7 +5405,7 @@
       <c r="A346" s="7"/>
       <c r="B346" s="8"/>
       <c r="C346" s="9"/>
-      <c r="D346" s="15"/>
+      <c r="D346" s="16"/>
       <c r="E346" s="10"/>
       <c r="F346" s="10"/>
       <c r="G346" s="11"/>
@@ -5416,7 +5419,7 @@
       <c r="A347" s="7"/>
       <c r="B347" s="8"/>
       <c r="C347" s="9"/>
-      <c r="D347" s="15"/>
+      <c r="D347" s="16"/>
       <c r="E347" s="10"/>
       <c r="F347" s="10"/>
       <c r="G347" s="11"/>
@@ -5430,7 +5433,7 @@
       <c r="A348" s="7"/>
       <c r="B348" s="8"/>
       <c r="C348" s="9"/>
-      <c r="D348" s="15"/>
+      <c r="D348" s="16"/>
       <c r="E348" s="10"/>
       <c r="F348" s="10"/>
       <c r="G348" s="11"/>
@@ -5444,7 +5447,7 @@
       <c r="A349" s="7"/>
       <c r="B349" s="8"/>
       <c r="C349" s="9"/>
-      <c r="D349" s="15"/>
+      <c r="D349" s="16"/>
       <c r="E349" s="10"/>
       <c r="F349" s="10"/>
       <c r="G349" s="11"/>
@@ -5458,7 +5461,7 @@
       <c r="A350" s="7"/>
       <c r="B350" s="8"/>
       <c r="C350" s="9"/>
-      <c r="D350" s="15"/>
+      <c r="D350" s="16"/>
       <c r="E350" s="10"/>
       <c r="F350" s="10"/>
       <c r="G350" s="11"/>
@@ -5472,7 +5475,7 @@
       <c r="A351" s="7"/>
       <c r="B351" s="8"/>
       <c r="C351" s="9"/>
-      <c r="D351" s="15"/>
+      <c r="D351" s="16"/>
       <c r="E351" s="10"/>
       <c r="F351" s="10"/>
       <c r="G351" s="11"/>
@@ -5486,7 +5489,7 @@
       <c r="A352" s="7"/>
       <c r="B352" s="8"/>
       <c r="C352" s="9"/>
-      <c r="D352" s="15"/>
+      <c r="D352" s="16"/>
       <c r="E352" s="10"/>
       <c r="F352" s="10"/>
       <c r="G352" s="11"/>
@@ -5500,7 +5503,7 @@
       <c r="A353" s="7"/>
       <c r="B353" s="8"/>
       <c r="C353" s="9"/>
-      <c r="D353" s="15"/>
+      <c r="D353" s="16"/>
       <c r="E353" s="10"/>
       <c r="F353" s="10"/>
       <c r="G353" s="11"/>
@@ -5514,7 +5517,7 @@
       <c r="A354" s="7"/>
       <c r="B354" s="8"/>
       <c r="C354" s="9"/>
-      <c r="D354" s="15"/>
+      <c r="D354" s="16"/>
       <c r="E354" s="10"/>
       <c r="F354" s="10"/>
       <c r="G354" s="11"/>
@@ -5528,7 +5531,7 @@
       <c r="A355" s="7"/>
       <c r="B355" s="8"/>
       <c r="C355" s="9"/>
-      <c r="D355" s="15"/>
+      <c r="D355" s="16"/>
       <c r="E355" s="10"/>
       <c r="F355" s="10"/>
       <c r="G355" s="11"/>
@@ -5542,7 +5545,7 @@
       <c r="A356" s="7"/>
       <c r="B356" s="8"/>
       <c r="C356" s="9"/>
-      <c r="D356" s="15"/>
+      <c r="D356" s="16"/>
       <c r="E356" s="10"/>
       <c r="F356" s="10"/>
       <c r="G356" s="11"/>
@@ -5556,7 +5559,7 @@
       <c r="A357" s="7"/>
       <c r="B357" s="8"/>
       <c r="C357" s="9"/>
-      <c r="D357" s="15"/>
+      <c r="D357" s="16"/>
       <c r="E357" s="10"/>
       <c r="F357" s="10"/>
       <c r="G357" s="11"/>
@@ -5570,7 +5573,7 @@
       <c r="A358" s="7"/>
       <c r="B358" s="8"/>
       <c r="C358" s="9"/>
-      <c r="D358" s="15"/>
+      <c r="D358" s="16"/>
       <c r="E358" s="10"/>
       <c r="F358" s="10"/>
       <c r="G358" s="11"/>
@@ -5584,7 +5587,7 @@
       <c r="A359" s="7"/>
       <c r="B359" s="8"/>
       <c r="C359" s="9"/>
-      <c r="D359" s="15"/>
+      <c r="D359" s="16"/>
       <c r="E359" s="10"/>
       <c r="F359" s="10"/>
       <c r="G359" s="11"/>
@@ -5598,7 +5601,7 @@
       <c r="A360" s="7"/>
       <c r="B360" s="8"/>
       <c r="C360" s="9"/>
-      <c r="D360" s="15"/>
+      <c r="D360" s="16"/>
       <c r="E360" s="10"/>
       <c r="F360" s="10"/>
       <c r="G360" s="11"/>
@@ -5612,7 +5615,7 @@
       <c r="A361" s="7"/>
       <c r="B361" s="8"/>
       <c r="C361" s="9"/>
-      <c r="D361" s="15"/>
+      <c r="D361" s="16"/>
       <c r="E361" s="10"/>
       <c r="F361" s="10"/>
       <c r="G361" s="11"/>
@@ -5626,7 +5629,7 @@
       <c r="A362" s="7"/>
       <c r="B362" s="8"/>
       <c r="C362" s="9"/>
-      <c r="D362" s="15"/>
+      <c r="D362" s="16"/>
       <c r="E362" s="10"/>
       <c r="F362" s="10"/>
       <c r="G362" s="11"/>
@@ -5640,7 +5643,7 @@
       <c r="A363" s="7"/>
       <c r="B363" s="8"/>
       <c r="C363" s="9"/>
-      <c r="D363" s="15"/>
+      <c r="D363" s="16"/>
       <c r="E363" s="10"/>
       <c r="F363" s="10"/>
       <c r="G363" s="11"/>
@@ -5654,7 +5657,7 @@
       <c r="A364" s="7"/>
       <c r="B364" s="8"/>
       <c r="C364" s="9"/>
-      <c r="D364" s="15"/>
+      <c r="D364" s="16"/>
       <c r="E364" s="10"/>
       <c r="F364" s="10"/>
       <c r="G364" s="11"/>
@@ -5668,7 +5671,7 @@
       <c r="A365" s="7"/>
       <c r="B365" s="8"/>
       <c r="C365" s="9"/>
-      <c r="D365" s="15"/>
+      <c r="D365" s="16"/>
       <c r="E365" s="10"/>
       <c r="F365" s="10"/>
       <c r="G365" s="11"/>
@@ -5682,7 +5685,7 @@
       <c r="A366" s="7"/>
       <c r="B366" s="8"/>
       <c r="C366" s="9"/>
-      <c r="D366" s="15"/>
+      <c r="D366" s="16"/>
       <c r="E366" s="10"/>
       <c r="F366" s="10"/>
       <c r="G366" s="11"/>
@@ -5696,7 +5699,7 @@
       <c r="A367" s="7"/>
       <c r="B367" s="8"/>
       <c r="C367" s="9"/>
-      <c r="D367" s="15"/>
+      <c r="D367" s="16"/>
       <c r="E367" s="10"/>
       <c r="F367" s="10"/>
       <c r="G367" s="11"/>
@@ -5710,7 +5713,7 @@
       <c r="A368" s="7"/>
       <c r="B368" s="8"/>
       <c r="C368" s="9"/>
-      <c r="D368" s="15"/>
+      <c r="D368" s="16"/>
       <c r="E368" s="10"/>
       <c r="F368" s="10"/>
       <c r="G368" s="11"/>
@@ -5724,7 +5727,7 @@
       <c r="A369" s="7"/>
       <c r="B369" s="8"/>
       <c r="C369" s="9"/>
-      <c r="D369" s="15"/>
+      <c r="D369" s="16"/>
       <c r="E369" s="10"/>
       <c r="F369" s="10"/>
       <c r="G369" s="11"/>
@@ -5738,7 +5741,7 @@
       <c r="A370" s="7"/>
       <c r="B370" s="8"/>
       <c r="C370" s="9"/>
-      <c r="D370" s="15"/>
+      <c r="D370" s="16"/>
       <c r="E370" s="10"/>
       <c r="F370" s="10"/>
       <c r="G370" s="11"/>
@@ -5752,7 +5755,7 @@
       <c r="A371" s="7"/>
       <c r="B371" s="8"/>
       <c r="C371" s="9"/>
-      <c r="D371" s="15"/>
+      <c r="D371" s="16"/>
       <c r="E371" s="10"/>
       <c r="F371" s="10"/>
       <c r="G371" s="11"/>
@@ -5766,7 +5769,7 @@
       <c r="A372" s="7"/>
       <c r="B372" s="8"/>
       <c r="C372" s="9"/>
-      <c r="D372" s="15"/>
+      <c r="D372" s="16"/>
       <c r="E372" s="10"/>
       <c r="F372" s="10"/>
       <c r="G372" s="11"/>
@@ -5780,7 +5783,7 @@
       <c r="A373" s="7"/>
       <c r="B373" s="8"/>
       <c r="C373" s="9"/>
-      <c r="D373" s="15"/>
+      <c r="D373" s="16"/>
       <c r="E373" s="10"/>
       <c r="F373" s="10"/>
       <c r="G373" s="11"/>
@@ -5794,7 +5797,7 @@
       <c r="A374" s="7"/>
       <c r="B374" s="8"/>
       <c r="C374" s="9"/>
-      <c r="D374" s="15"/>
+      <c r="D374" s="16"/>
       <c r="E374" s="10"/>
       <c r="F374" s="10"/>
       <c r="G374" s="11"/>
@@ -5808,7 +5811,7 @@
       <c r="A375" s="7"/>
       <c r="B375" s="8"/>
       <c r="C375" s="9"/>
-      <c r="D375" s="15"/>
+      <c r="D375" s="16"/>
       <c r="E375" s="10"/>
       <c r="F375" s="10"/>
       <c r="G375" s="11"/>
@@ -5822,7 +5825,7 @@
       <c r="A376" s="7"/>
       <c r="B376" s="8"/>
       <c r="C376" s="9"/>
-      <c r="D376" s="15"/>
+      <c r="D376" s="16"/>
       <c r="E376" s="10"/>
       <c r="F376" s="10"/>
       <c r="G376" s="11"/>
@@ -5836,7 +5839,7 @@
       <c r="A377" s="7"/>
       <c r="B377" s="8"/>
       <c r="C377" s="9"/>
-      <c r="D377" s="15"/>
+      <c r="D377" s="16"/>
       <c r="E377" s="10"/>
       <c r="F377" s="10"/>
       <c r="G377" s="11"/>
@@ -5850,7 +5853,7 @@
       <c r="A378" s="7"/>
       <c r="B378" s="8"/>
       <c r="C378" s="9"/>
-      <c r="D378" s="15"/>
+      <c r="D378" s="16"/>
       <c r="E378" s="10"/>
       <c r="F378" s="10"/>
       <c r="G378" s="11"/>
@@ -5864,7 +5867,7 @@
       <c r="A379" s="7"/>
       <c r="B379" s="8"/>
       <c r="C379" s="9"/>
-      <c r="D379" s="15"/>
+      <c r="D379" s="16"/>
       <c r="E379" s="10"/>
       <c r="F379" s="10"/>
       <c r="G379" s="11"/>
@@ -5878,7 +5881,7 @@
       <c r="A380" s="7"/>
       <c r="B380" s="8"/>
       <c r="C380" s="9"/>
-      <c r="D380" s="15"/>
+      <c r="D380" s="16"/>
       <c r="E380" s="10"/>
       <c r="F380" s="10"/>
       <c r="G380" s="11"/>
@@ -5892,7 +5895,7 @@
       <c r="A381" s="7"/>
       <c r="B381" s="8"/>
       <c r="C381" s="9"/>
-      <c r="D381" s="15"/>
+      <c r="D381" s="16"/>
       <c r="E381" s="10"/>
       <c r="F381" s="10"/>
       <c r="G381" s="11"/>
@@ -5906,7 +5909,7 @@
       <c r="A382" s="7"/>
       <c r="B382" s="8"/>
       <c r="C382" s="9"/>
-      <c r="D382" s="15"/>
+      <c r="D382" s="16"/>
       <c r="E382" s="10"/>
       <c r="F382" s="10"/>
       <c r="G382" s="11"/>
@@ -5920,7 +5923,7 @@
       <c r="A383" s="7"/>
       <c r="B383" s="8"/>
       <c r="C383" s="9"/>
-      <c r="D383" s="15"/>
+      <c r="D383" s="16"/>
       <c r="E383" s="10"/>
       <c r="F383" s="10"/>
       <c r="G383" s="11"/>
@@ -5934,7 +5937,7 @@
       <c r="A384" s="7"/>
       <c r="B384" s="8"/>
       <c r="C384" s="9"/>
-      <c r="D384" s="15"/>
+      <c r="D384" s="16"/>
       <c r="E384" s="10"/>
       <c r="F384" s="10"/>
       <c r="G384" s="11"/>
@@ -5948,7 +5951,7 @@
       <c r="A385" s="7"/>
       <c r="B385" s="8"/>
       <c r="C385" s="9"/>
-      <c r="D385" s="15"/>
+      <c r="D385" s="16"/>
       <c r="E385" s="10"/>
       <c r="F385" s="10"/>
       <c r="G385" s="11"/>
@@ -5962,7 +5965,7 @@
       <c r="A386" s="7"/>
       <c r="B386" s="8"/>
       <c r="C386" s="9"/>
-      <c r="D386" s="15"/>
+      <c r="D386" s="16"/>
       <c r="E386" s="10"/>
       <c r="F386" s="10"/>
       <c r="G386" s="11"/>
@@ -5976,7 +5979,7 @@
       <c r="A387" s="7"/>
       <c r="B387" s="8"/>
       <c r="C387" s="9"/>
-      <c r="D387" s="15"/>
+      <c r="D387" s="16"/>
       <c r="E387" s="10"/>
       <c r="F387" s="10"/>
       <c r="G387" s="11"/>
@@ -5990,7 +5993,7 @@
       <c r="A388" s="7"/>
       <c r="B388" s="8"/>
       <c r="C388" s="9"/>
-      <c r="D388" s="15"/>
+      <c r="D388" s="16"/>
       <c r="E388" s="10"/>
       <c r="F388" s="10"/>
       <c r="G388" s="11"/>
@@ -6004,7 +6007,7 @@
       <c r="A389" s="7"/>
       <c r="B389" s="8"/>
       <c r="C389" s="9"/>
-      <c r="D389" s="15"/>
+      <c r="D389" s="16"/>
       <c r="E389" s="10"/>
       <c r="F389" s="10"/>
       <c r="G389" s="11"/>
@@ -6018,7 +6021,7 @@
       <c r="A390" s="7"/>
       <c r="B390" s="8"/>
       <c r="C390" s="9"/>
-      <c r="D390" s="15"/>
+      <c r="D390" s="16"/>
       <c r="E390" s="10"/>
       <c r="F390" s="10"/>
       <c r="G390" s="11"/>
@@ -6032,7 +6035,7 @@
       <c r="A391" s="7"/>
       <c r="B391" s="8"/>
       <c r="C391" s="9"/>
-      <c r="D391" s="15"/>
+      <c r="D391" s="16"/>
       <c r="E391" s="10"/>
       <c r="F391" s="10"/>
       <c r="G391" s="11"/>
@@ -6046,7 +6049,7 @@
       <c r="A392" s="7"/>
       <c r="B392" s="8"/>
       <c r="C392" s="9"/>
-      <c r="D392" s="15"/>
+      <c r="D392" s="16"/>
       <c r="E392" s="10"/>
       <c r="F392" s="10"/>
       <c r="G392" s="11"/>
@@ -6060,7 +6063,7 @@
       <c r="A393" s="7"/>
       <c r="B393" s="8"/>
       <c r="C393" s="9"/>
-      <c r="D393" s="15"/>
+      <c r="D393" s="16"/>
       <c r="E393" s="10"/>
       <c r="F393" s="10"/>
       <c r="G393" s="11"/>
@@ -6074,7 +6077,7 @@
       <c r="A394" s="7"/>
       <c r="B394" s="8"/>
       <c r="C394" s="9"/>
-      <c r="D394" s="15"/>
+      <c r="D394" s="16"/>
       <c r="E394" s="10"/>
       <c r="F394" s="10"/>
       <c r="G394" s="11"/>
@@ -6088,7 +6091,7 @@
       <c r="A395" s="7"/>
       <c r="B395" s="8"/>
       <c r="C395" s="9"/>
-      <c r="D395" s="15"/>
+      <c r="D395" s="16"/>
       <c r="E395" s="10"/>
       <c r="F395" s="10"/>
       <c r="G395" s="11"/>
@@ -6102,7 +6105,7 @@
       <c r="A396" s="7"/>
       <c r="B396" s="8"/>
       <c r="C396" s="9"/>
-      <c r="D396" s="15"/>
+      <c r="D396" s="16"/>
       <c r="E396" s="10"/>
       <c r="F396" s="10"/>
       <c r="G396" s="11"/>
@@ -6116,7 +6119,7 @@
       <c r="A397" s="7"/>
       <c r="B397" s="8"/>
       <c r="C397" s="9"/>
-      <c r="D397" s="15"/>
+      <c r="D397" s="16"/>
       <c r="E397" s="10"/>
       <c r="F397" s="10"/>
       <c r="G397" s="11"/>
@@ -6130,7 +6133,7 @@
       <c r="A398" s="7"/>
       <c r="B398" s="8"/>
       <c r="C398" s="9"/>
-      <c r="D398" s="15"/>
+      <c r="D398" s="16"/>
       <c r="E398" s="10"/>
       <c r="F398" s="10"/>
       <c r="G398" s="11"/>
@@ -6144,7 +6147,7 @@
       <c r="A399" s="7"/>
       <c r="B399" s="8"/>
       <c r="C399" s="9"/>
-      <c r="D399" s="15"/>
+      <c r="D399" s="16"/>
       <c r="E399" s="10"/>
       <c r="F399" s="10"/>
       <c r="G399" s="11"/>
@@ -6158,7 +6161,7 @@
       <c r="A400" s="7"/>
       <c r="B400" s="8"/>
       <c r="C400" s="9"/>
-      <c r="D400" s="15"/>
+      <c r="D400" s="16"/>
       <c r="E400" s="10"/>
       <c r="F400" s="10"/>
       <c r="G400" s="11"/>
@@ -6172,7 +6175,7 @@
       <c r="A401" s="7"/>
       <c r="B401" s="8"/>
       <c r="C401" s="9"/>
-      <c r="D401" s="15"/>
+      <c r="D401" s="16"/>
       <c r="E401" s="10"/>
       <c r="F401" s="10"/>
       <c r="G401" s="11"/>
@@ -6186,7 +6189,7 @@
       <c r="A402" s="7"/>
       <c r="B402" s="8"/>
       <c r="C402" s="9"/>
-      <c r="D402" s="15"/>
+      <c r="D402" s="16"/>
       <c r="E402" s="10"/>
       <c r="F402" s="10"/>
       <c r="G402" s="11"/>
@@ -6200,7 +6203,7 @@
       <c r="A403" s="7"/>
       <c r="B403" s="8"/>
       <c r="C403" s="9"/>
-      <c r="D403" s="15"/>
+      <c r="D403" s="16"/>
       <c r="E403" s="10"/>
       <c r="F403" s="10"/>
       <c r="G403" s="11"/>
@@ -6214,7 +6217,7 @@
       <c r="A404" s="7"/>
       <c r="B404" s="8"/>
       <c r="C404" s="9"/>
-      <c r="D404" s="15"/>
+      <c r="D404" s="16"/>
       <c r="E404" s="10"/>
       <c r="F404" s="10"/>
       <c r="G404" s="11"/>
@@ -6228,7 +6231,7 @@
       <c r="A405" s="7"/>
       <c r="B405" s="8"/>
       <c r="C405" s="9"/>
-      <c r="D405" s="15"/>
+      <c r="D405" s="16"/>
       <c r="E405" s="10"/>
       <c r="F405" s="10"/>
       <c r="G405" s="11"/>
@@ -6242,7 +6245,7 @@
       <c r="A406" s="7"/>
       <c r="B406" s="8"/>
       <c r="C406" s="9"/>
-      <c r="D406" s="15"/>
+      <c r="D406" s="16"/>
       <c r="E406" s="10"/>
       <c r="F406" s="10"/>
       <c r="G406" s="11"/>
@@ -6256,7 +6259,7 @@
       <c r="A407" s="7"/>
       <c r="B407" s="8"/>
       <c r="C407" s="9"/>
-      <c r="D407" s="15"/>
+      <c r="D407" s="16"/>
       <c r="E407" s="10"/>
       <c r="F407" s="10"/>
       <c r="G407" s="11"/>
@@ -6270,7 +6273,7 @@
       <c r="A408" s="7"/>
       <c r="B408" s="8"/>
       <c r="C408" s="9"/>
-      <c r="D408" s="15"/>
+      <c r="D408" s="16"/>
       <c r="E408" s="10"/>
       <c r="F408" s="10"/>
       <c r="G408" s="11"/>
@@ -6284,7 +6287,7 @@
       <c r="A409" s="7"/>
       <c r="B409" s="8"/>
       <c r="C409" s="9"/>
-      <c r="D409" s="15"/>
+      <c r="D409" s="16"/>
       <c r="E409" s="10"/>
       <c r="F409" s="10"/>
       <c r="G409" s="11"/>
@@ -6298,7 +6301,7 @@
       <c r="A410" s="7"/>
       <c r="B410" s="8"/>
       <c r="C410" s="9"/>
-      <c r="D410" s="15"/>
+      <c r="D410" s="16"/>
       <c r="E410" s="10"/>
       <c r="F410" s="10"/>
       <c r="G410" s="11"/>
@@ -6312,7 +6315,7 @@
       <c r="A411" s="7"/>
       <c r="B411" s="8"/>
       <c r="C411" s="9"/>
-      <c r="D411" s="15"/>
+      <c r="D411" s="16"/>
       <c r="E411" s="10"/>
       <c r="F411" s="10"/>
       <c r="G411" s="11"/>
@@ -6326,7 +6329,7 @@
       <c r="A412" s="7"/>
       <c r="B412" s="8"/>
       <c r="C412" s="9"/>
-      <c r="D412" s="15"/>
+      <c r="D412" s="16"/>
       <c r="E412" s="10"/>
       <c r="F412" s="10"/>
       <c r="G412" s="11"/>
@@ -6340,7 +6343,7 @@
       <c r="A413" s="7"/>
       <c r="B413" s="8"/>
       <c r="C413" s="9"/>
-      <c r="D413" s="15"/>
+      <c r="D413" s="16"/>
       <c r="E413" s="10"/>
       <c r="F413" s="10"/>
       <c r="G413" s="11"/>
@@ -6354,7 +6357,7 @@
       <c r="A414" s="7"/>
       <c r="B414" s="8"/>
       <c r="C414" s="9"/>
-      <c r="D414" s="15"/>
+      <c r="D414" s="16"/>
       <c r="E414" s="10"/>
       <c r="F414" s="10"/>
       <c r="G414" s="11"/>
@@ -6368,7 +6371,7 @@
       <c r="A415" s="7"/>
       <c r="B415" s="8"/>
       <c r="C415" s="9"/>
-      <c r="D415" s="15"/>
+      <c r="D415" s="16"/>
       <c r="E415" s="10"/>
       <c r="F415" s="10"/>
       <c r="G415" s="11"/>
@@ -6382,7 +6385,7 @@
       <c r="A416" s="7"/>
       <c r="B416" s="8"/>
       <c r="C416" s="9"/>
-      <c r="D416" s="15"/>
+      <c r="D416" s="16"/>
       <c r="E416" s="10"/>
       <c r="F416" s="10"/>
       <c r="G416" s="11"/>
@@ -6396,7 +6399,7 @@
       <c r="A417" s="7"/>
       <c r="B417" s="8"/>
       <c r="C417" s="9"/>
-      <c r="D417" s="15"/>
+      <c r="D417" s="16"/>
       <c r="E417" s="10"/>
       <c r="F417" s="10"/>
       <c r="G417" s="11"/>
@@ -6410,7 +6413,7 @@
       <c r="A418" s="7"/>
       <c r="B418" s="8"/>
       <c r="C418" s="9"/>
-      <c r="D418" s="15"/>
+      <c r="D418" s="16"/>
       <c r="E418" s="10"/>
       <c r="F418" s="10"/>
       <c r="G418" s="11"/>
@@ -6424,7 +6427,7 @@
       <c r="A419" s="7"/>
       <c r="B419" s="8"/>
       <c r="C419" s="9"/>
-      <c r="D419" s="15"/>
+      <c r="D419" s="16"/>
       <c r="E419" s="10"/>
       <c r="F419" s="10"/>
       <c r="G419" s="11"/>
@@ -6438,7 +6441,7 @@
       <c r="A420" s="7"/>
       <c r="B420" s="8"/>
       <c r="C420" s="9"/>
-      <c r="D420" s="15"/>
+      <c r="D420" s="16"/>
       <c r="E420" s="10"/>
       <c r="F420" s="10"/>
       <c r="G420" s="11"/>
@@ -6452,7 +6455,7 @@
       <c r="A421" s="7"/>
       <c r="B421" s="8"/>
       <c r="C421" s="9"/>
-      <c r="D421" s="15"/>
+      <c r="D421" s="16"/>
       <c r="E421" s="10"/>
       <c r="F421" s="10"/>
       <c r="G421" s="11"/>
@@ -6466,7 +6469,7 @@
       <c r="A422" s="7"/>
       <c r="B422" s="8"/>
       <c r="C422" s="9"/>
-      <c r="D422" s="15"/>
+      <c r="D422" s="16"/>
       <c r="E422" s="10"/>
       <c r="F422" s="10"/>
       <c r="G422" s="11"/>
@@ -6480,7 +6483,7 @@
       <c r="A423" s="7"/>
       <c r="B423" s="8"/>
       <c r="C423" s="9"/>
-      <c r="D423" s="15"/>
+      <c r="D423" s="16"/>
       <c r="E423" s="10"/>
       <c r="F423" s="10"/>
       <c r="G423" s="11"/>
@@ -6494,7 +6497,7 @@
       <c r="A424" s="7"/>
       <c r="B424" s="8"/>
       <c r="C424" s="9"/>
-      <c r="D424" s="15"/>
+      <c r="D424" s="16"/>
       <c r="E424" s="10"/>
       <c r="F424" s="10"/>
       <c r="G424" s="11"/>
@@ -6508,7 +6511,7 @@
       <c r="A425" s="7"/>
       <c r="B425" s="8"/>
       <c r="C425" s="9"/>
-      <c r="D425" s="15"/>
+      <c r="D425" s="16"/>
       <c r="E425" s="10"/>
       <c r="F425" s="10"/>
       <c r="G425" s="11"/>
@@ -6522,7 +6525,7 @@
       <c r="A426" s="7"/>
       <c r="B426" s="8"/>
       <c r="C426" s="9"/>
-      <c r="D426" s="15"/>
+      <c r="D426" s="16"/>
       <c r="E426" s="10"/>
       <c r="F426" s="10"/>
       <c r="G426" s="11"/>
@@ -6536,7 +6539,7 @@
       <c r="A427" s="7"/>
       <c r="B427" s="8"/>
       <c r="C427" s="9"/>
-      <c r="D427" s="15"/>
+      <c r="D427" s="16"/>
       <c r="E427" s="10"/>
       <c r="F427" s="10"/>
       <c r="G427" s="11"/>
@@ -6550,7 +6553,7 @@
       <c r="A428" s="7"/>
       <c r="B428" s="8"/>
       <c r="C428" s="9"/>
-      <c r="D428" s="15"/>
+      <c r="D428" s="16"/>
       <c r="E428" s="10"/>
       <c r="F428" s="10"/>
       <c r="G428" s="11"/>
@@ -6564,7 +6567,7 @@
       <c r="A429" s="7"/>
       <c r="B429" s="8"/>
       <c r="C429" s="9"/>
-      <c r="D429" s="15"/>
+      <c r="D429" s="16"/>
       <c r="E429" s="10"/>
       <c r="F429" s="10"/>
       <c r="G429" s="11"/>
@@ -6578,7 +6581,7 @@
       <c r="A430" s="7"/>
       <c r="B430" s="8"/>
       <c r="C430" s="9"/>
-      <c r="D430" s="15"/>
+      <c r="D430" s="16"/>
       <c r="E430" s="10"/>
       <c r="F430" s="10"/>
       <c r="G430" s="11"/>
@@ -6592,7 +6595,7 @@
       <c r="A431" s="7"/>
       <c r="B431" s="8"/>
       <c r="C431" s="9"/>
-      <c r="D431" s="15"/>
+      <c r="D431" s="16"/>
       <c r="E431" s="10"/>
       <c r="F431" s="10"/>
       <c r="G431" s="11"/>
@@ -6606,7 +6609,7 @@
       <c r="A432" s="7"/>
       <c r="B432" s="8"/>
       <c r="C432" s="9"/>
-      <c r="D432" s="15"/>
+      <c r="D432" s="16"/>
       <c r="E432" s="10"/>
       <c r="F432" s="10"/>
       <c r="G432" s="11"/>
@@ -6620,7 +6623,7 @@
       <c r="A433" s="7"/>
       <c r="B433" s="8"/>
       <c r="C433" s="9"/>
-      <c r="D433" s="15"/>
+      <c r="D433" s="16"/>
       <c r="E433" s="10"/>
       <c r="F433" s="10"/>
       <c r="G433" s="11"/>
@@ -6634,7 +6637,7 @@
       <c r="A434" s="7"/>
       <c r="B434" s="8"/>
       <c r="C434" s="9"/>
-      <c r="D434" s="15"/>
+      <c r="D434" s="16"/>
       <c r="E434" s="10"/>
       <c r="F434" s="10"/>
       <c r="G434" s="11"/>
@@ -6648,7 +6651,7 @@
       <c r="A435" s="7"/>
       <c r="B435" s="8"/>
       <c r="C435" s="9"/>
-      <c r="D435" s="15"/>
+      <c r="D435" s="16"/>
       <c r="E435" s="10"/>
       <c r="F435" s="10"/>
       <c r="G435" s="11"/>
@@ -6662,7 +6665,7 @@
       <c r="A436" s="7"/>
       <c r="B436" s="8"/>
       <c r="C436" s="9"/>
-      <c r="D436" s="15"/>
+      <c r="D436" s="16"/>
       <c r="E436" s="10"/>
       <c r="F436" s="10"/>
       <c r="G436" s="11"/>
@@ -6676,7 +6679,7 @@
       <c r="A437" s="7"/>
       <c r="B437" s="8"/>
       <c r="C437" s="9"/>
-      <c r="D437" s="15"/>
+      <c r="D437" s="16"/>
       <c r="E437" s="10"/>
       <c r="F437" s="10"/>
       <c r="G437" s="11"/>
@@ -6690,7 +6693,7 @@
       <c r="A438" s="7"/>
       <c r="B438" s="8"/>
       <c r="C438" s="9"/>
-      <c r="D438" s="15"/>
+      <c r="D438" s="16"/>
       <c r="E438" s="10"/>
       <c r="F438" s="10"/>
       <c r="G438" s="11"/>
@@ -6704,7 +6707,7 @@
       <c r="A439" s="7"/>
       <c r="B439" s="8"/>
       <c r="C439" s="9"/>
-      <c r="D439" s="15"/>
+      <c r="D439" s="16"/>
       <c r="E439" s="10"/>
       <c r="F439" s="10"/>
       <c r="G439" s="11"/>
@@ -6718,7 +6721,7 @@
       <c r="A440" s="7"/>
       <c r="B440" s="8"/>
       <c r="C440" s="9"/>
-      <c r="D440" s="15"/>
+      <c r="D440" s="16"/>
       <c r="E440" s="10"/>
       <c r="F440" s="10"/>
       <c r="G440" s="11"/>
@@ -6732,7 +6735,7 @@
       <c r="A441" s="7"/>
       <c r="B441" s="8"/>
       <c r="C441" s="9"/>
-      <c r="D441" s="15"/>
+      <c r="D441" s="16"/>
       <c r="E441" s="10"/>
       <c r="F441" s="10"/>
       <c r="G441" s="11"/>
@@ -6746,7 +6749,7 @@
       <c r="A442" s="7"/>
       <c r="B442" s="8"/>
       <c r="C442" s="9"/>
-      <c r="D442" s="15"/>
+      <c r="D442" s="16"/>
       <c r="E442" s="10"/>
       <c r="F442" s="10"/>
       <c r="G442" s="11"/>
@@ -6760,7 +6763,7 @@
       <c r="A443" s="7"/>
       <c r="B443" s="8"/>
       <c r="C443" s="9"/>
-      <c r="D443" s="15"/>
+      <c r="D443" s="16"/>
       <c r="E443" s="10"/>
       <c r="F443" s="10"/>
       <c r="G443" s="11"/>
@@ -6774,7 +6777,7 @@
       <c r="A444" s="7"/>
       <c r="B444" s="8"/>
       <c r="C444" s="9"/>
-      <c r="D444" s="15"/>
+      <c r="D444" s="16"/>
       <c r="E444" s="10"/>
       <c r="F444" s="10"/>
       <c r="G444" s="11"/>
@@ -6788,7 +6791,7 @@
       <c r="A445" s="7"/>
       <c r="B445" s="8"/>
       <c r="C445" s="9"/>
-      <c r="D445" s="15"/>
+      <c r="D445" s="16"/>
       <c r="E445" s="10"/>
       <c r="F445" s="10"/>
       <c r="G445" s="11"/>
@@ -6802,7 +6805,7 @@
       <c r="A446" s="7"/>
       <c r="B446" s="8"/>
       <c r="C446" s="9"/>
-      <c r="D446" s="15"/>
+      <c r="D446" s="16"/>
       <c r="E446" s="10"/>
       <c r="F446" s="10"/>
       <c r="G446" s="11"/>
@@ -6816,7 +6819,7 @@
       <c r="A447" s="7"/>
       <c r="B447" s="8"/>
       <c r="C447" s="9"/>
-      <c r="D447" s="15"/>
+      <c r="D447" s="16"/>
       <c r="E447" s="10"/>
       <c r="F447" s="10"/>
       <c r="G447" s="11"/>
@@ -6830,7 +6833,7 @@
       <c r="A448" s="7"/>
       <c r="B448" s="8"/>
       <c r="C448" s="9"/>
-      <c r="D448" s="15"/>
+      <c r="D448" s="16"/>
       <c r="E448" s="10"/>
       <c r="F448" s="10"/>
       <c r="G448" s="11"/>
@@ -6844,7 +6847,7 @@
       <c r="A449" s="7"/>
       <c r="B449" s="8"/>
       <c r="C449" s="9"/>
-      <c r="D449" s="15"/>
+      <c r="D449" s="16"/>
       <c r="E449" s="10"/>
       <c r="F449" s="10"/>
       <c r="G449" s="11"/>
@@ -6858,7 +6861,7 @@
       <c r="A450" s="7"/>
       <c r="B450" s="8"/>
       <c r="C450" s="9"/>
-      <c r="D450" s="15"/>
+      <c r="D450" s="16"/>
       <c r="E450" s="10"/>
       <c r="F450" s="10"/>
       <c r="G450" s="11"/>
@@ -6872,7 +6875,7 @@
       <c r="A451" s="7"/>
       <c r="B451" s="8"/>
       <c r="C451" s="9"/>
-      <c r="D451" s="15"/>
+      <c r="D451" s="16"/>
       <c r="E451" s="10"/>
       <c r="F451" s="10"/>
       <c r="G451" s="11"/>
@@ -6886,7 +6889,7 @@
       <c r="A452" s="7"/>
       <c r="B452" s="8"/>
       <c r="C452" s="9"/>
-      <c r="D452" s="15"/>
+      <c r="D452" s="16"/>
       <c r="E452" s="10"/>
       <c r="F452" s="10"/>
       <c r="G452" s="11"/>
@@ -6900,7 +6903,7 @@
       <c r="A453" s="7"/>
       <c r="B453" s="8"/>
       <c r="C453" s="9"/>
-      <c r="D453" s="15"/>
+      <c r="D453" s="16"/>
       <c r="E453" s="10"/>
       <c r="F453" s="10"/>
       <c r="G453" s="11"/>
@@ -6914,7 +6917,7 @@
       <c r="A454" s="7"/>
       <c r="B454" s="8"/>
       <c r="C454" s="9"/>
-      <c r="D454" s="15"/>
+      <c r="D454" s="16"/>
       <c r="E454" s="10"/>
       <c r="F454" s="10"/>
       <c r="G454" s="11"/>
@@ -6928,7 +6931,7 @@
       <c r="A455" s="7"/>
       <c r="B455" s="8"/>
       <c r="C455" s="9"/>
-      <c r="D455" s="15"/>
+      <c r="D455" s="16"/>
       <c r="E455" s="10"/>
       <c r="F455" s="10"/>
       <c r="G455" s="11"/>
@@ -6942,7 +6945,7 @@
       <c r="A456" s="7"/>
       <c r="B456" s="8"/>
       <c r="C456" s="9"/>
-      <c r="D456" s="15"/>
+      <c r="D456" s="16"/>
       <c r="E456" s="10"/>
       <c r="F456" s="10"/>
       <c r="G456" s="11"/>
@@ -6956,7 +6959,7 @@
       <c r="A457" s="7"/>
       <c r="B457" s="8"/>
       <c r="C457" s="9"/>
-      <c r="D457" s="15"/>
+      <c r="D457" s="16"/>
       <c r="E457" s="10"/>
       <c r="F457" s="10"/>
       <c r="G457" s="11"/>
@@ -6970,7 +6973,7 @@
       <c r="A458" s="7"/>
       <c r="B458" s="8"/>
       <c r="C458" s="9"/>
-      <c r="D458" s="15"/>
+      <c r="D458" s="16"/>
       <c r="E458" s="10"/>
       <c r="F458" s="10"/>
       <c r="G458" s="11"/>
@@ -6984,7 +6987,7 @@
       <c r="A459" s="7"/>
       <c r="B459" s="8"/>
       <c r="C459" s="9"/>
-      <c r="D459" s="15"/>
+      <c r="D459" s="16"/>
       <c r="E459" s="10"/>
       <c r="F459" s="10"/>
       <c r="G459" s="11"/>
@@ -6998,7 +7001,7 @@
       <c r="A460" s="7"/>
       <c r="B460" s="8"/>
       <c r="C460" s="9"/>
-      <c r="D460" s="15"/>
+      <c r="D460" s="16"/>
       <c r="E460" s="10"/>
       <c r="F460" s="10"/>
       <c r="G460" s="11"/>
@@ -7012,7 +7015,7 @@
       <c r="A461" s="7"/>
       <c r="B461" s="8"/>
       <c r="C461" s="9"/>
-      <c r="D461" s="15"/>
+      <c r="D461" s="16"/>
       <c r="E461" s="10"/>
       <c r="F461" s="10"/>
       <c r="G461" s="11"/>
@@ -7026,7 +7029,7 @@
       <c r="A462" s="7"/>
       <c r="B462" s="8"/>
       <c r="C462" s="9"/>
-      <c r="D462" s="15"/>
+      <c r="D462" s="16"/>
       <c r="E462" s="10"/>
       <c r="F462" s="10"/>
       <c r="G462" s="11"/>
@@ -7040,7 +7043,7 @@
       <c r="A463" s="7"/>
       <c r="B463" s="8"/>
       <c r="C463" s="9"/>
-      <c r="D463" s="15"/>
+      <c r="D463" s="16"/>
       <c r="E463" s="10"/>
       <c r="F463" s="10"/>
       <c r="G463" s="11"/>
@@ -7054,7 +7057,7 @@
       <c r="A464" s="7"/>
       <c r="B464" s="8"/>
       <c r="C464" s="9"/>
-      <c r="D464" s="15"/>
+      <c r="D464" s="16"/>
       <c r="E464" s="10"/>
       <c r="F464" s="10"/>
       <c r="G464" s="11"/>
@@ -7068,7 +7071,7 @@
       <c r="A465" s="7"/>
       <c r="B465" s="8"/>
       <c r="C465" s="9"/>
-      <c r="D465" s="15"/>
+      <c r="D465" s="16"/>
       <c r="E465" s="10"/>
       <c r="F465" s="10"/>
       <c r="G465" s="11"/>
@@ -7082,7 +7085,7 @@
       <c r="A466" s="7"/>
       <c r="B466" s="8"/>
       <c r="C466" s="9"/>
-      <c r="D466" s="15"/>
+      <c r="D466" s="16"/>
       <c r="E466" s="10"/>
       <c r="F466" s="10"/>
       <c r="G466" s="11"/>
@@ -7096,7 +7099,7 @@
       <c r="A467" s="7"/>
       <c r="B467" s="8"/>
       <c r="C467" s="9"/>
-      <c r="D467" s="15"/>
+      <c r="D467" s="16"/>
       <c r="E467" s="10"/>
       <c r="F467" s="10"/>
       <c r="G467" s="11"/>
@@ -7110,7 +7113,7 @@
       <c r="A468" s="7"/>
       <c r="B468" s="8"/>
       <c r="C468" s="9"/>
-      <c r="D468" s="15"/>
+      <c r="D468" s="16"/>
       <c r="E468" s="10"/>
       <c r="F468" s="10"/>
       <c r="G468" s="11"/>
@@ -7124,7 +7127,7 @@
       <c r="A469" s="7"/>
       <c r="B469" s="8"/>
       <c r="C469" s="9"/>
-      <c r="D469" s="15"/>
+      <c r="D469" s="16"/>
       <c r="E469" s="10"/>
       <c r="F469" s="10"/>
       <c r="G469" s="11"/>
@@ -7138,7 +7141,7 @@
       <c r="A470" s="7"/>
       <c r="B470" s="8"/>
       <c r="C470" s="9"/>
-      <c r="D470" s="15"/>
+      <c r="D470" s="16"/>
       <c r="E470" s="10"/>
       <c r="F470" s="10"/>
       <c r="G470" s="11"/>
@@ -7152,7 +7155,7 @@
       <c r="A471" s="7"/>
       <c r="B471" s="8"/>
       <c r="C471" s="9"/>
-      <c r="D471" s="15"/>
+      <c r="D471" s="16"/>
       <c r="E471" s="10"/>
       <c r="F471" s="10"/>
       <c r="G471" s="11"/>
@@ -7166,7 +7169,7 @@
       <c r="A472" s="7"/>
       <c r="B472" s="8"/>
       <c r="C472" s="9"/>
-      <c r="D472" s="15"/>
+      <c r="D472" s="16"/>
       <c r="E472" s="10"/>
       <c r="F472" s="10"/>
       <c r="G472" s="11"/>
@@ -7180,7 +7183,7 @@
       <c r="A473" s="7"/>
       <c r="B473" s="8"/>
       <c r="C473" s="9"/>
-      <c r="D473" s="15"/>
+      <c r="D473" s="16"/>
       <c r="E473" s="10"/>
       <c r="F473" s="10"/>
       <c r="G473" s="11"/>
@@ -7194,7 +7197,7 @@
       <c r="A474" s="7"/>
       <c r="B474" s="8"/>
       <c r="C474" s="9"/>
-      <c r="D474" s="15"/>
+      <c r="D474" s="16"/>
       <c r="E474" s="10"/>
       <c r="F474" s="10"/>
       <c r="G474" s="11"/>
@@ -7208,7 +7211,7 @@
       <c r="A475" s="7"/>
       <c r="B475" s="8"/>
       <c r="C475" s="9"/>
-      <c r="D475" s="15"/>
+      <c r="D475" s="16"/>
       <c r="E475" s="10"/>
       <c r="F475" s="10"/>
       <c r="G475" s="11"/>
@@ -7222,7 +7225,7 @@
       <c r="A476" s="7"/>
       <c r="B476" s="8"/>
       <c r="C476" s="9"/>
-      <c r="D476" s="15"/>
+      <c r="D476" s="16"/>
       <c r="E476" s="10"/>
       <c r="F476" s="10"/>
       <c r="G476" s="11"/>
@@ -7236,7 +7239,7 @@
       <c r="A477" s="7"/>
       <c r="B477" s="8"/>
       <c r="C477" s="9"/>
-      <c r="D477" s="15"/>
+      <c r="D477" s="16"/>
       <c r="E477" s="10"/>
       <c r="F477" s="10"/>
       <c r="G477" s="11"/>
@@ -7250,7 +7253,7 @@
       <c r="A478" s="7"/>
       <c r="B478" s="8"/>
       <c r="C478" s="9"/>
-      <c r="D478" s="15"/>
+      <c r="D478" s="16"/>
       <c r="E478" s="10"/>
       <c r="F478" s="10"/>
       <c r="G478" s="11"/>
@@ -7264,7 +7267,7 @@
       <c r="A479" s="7"/>
       <c r="B479" s="8"/>
       <c r="C479" s="9"/>
-      <c r="D479" s="15"/>
+      <c r="D479" s="16"/>
       <c r="E479" s="10"/>
       <c r="F479" s="10"/>
       <c r="G479" s="11"/>
@@ -7278,7 +7281,7 @@
       <c r="A480" s="7"/>
       <c r="B480" s="8"/>
       <c r="C480" s="9"/>
-      <c r="D480" s="15"/>
+      <c r="D480" s="16"/>
       <c r="E480" s="10"/>
       <c r="F480" s="10"/>
       <c r="G480" s="11"/>
@@ -7292,7 +7295,7 @@
       <c r="A481" s="7"/>
       <c r="B481" s="8"/>
       <c r="C481" s="9"/>
-      <c r="D481" s="15"/>
+      <c r="D481" s="16"/>
       <c r="E481" s="10"/>
       <c r="F481" s="10"/>
       <c r="G481" s="11"/>
@@ -7306,7 +7309,7 @@
       <c r="A482" s="7"/>
       <c r="B482" s="8"/>
       <c r="C482" s="9"/>
-      <c r="D482" s="15"/>
+      <c r="D482" s="16"/>
       <c r="E482" s="10"/>
       <c r="F482" s="10"/>
       <c r="G482" s="11"/>
@@ -7320,7 +7323,7 @@
       <c r="A483" s="7"/>
       <c r="B483" s="8"/>
       <c r="C483" s="9"/>
-      <c r="D483" s="15"/>
+      <c r="D483" s="16"/>
       <c r="E483" s="10"/>
       <c r="F483" s="10"/>
       <c r="G483" s="11"/>
@@ -7334,7 +7337,7 @@
       <c r="A484" s="7"/>
       <c r="B484" s="8"/>
       <c r="C484" s="9"/>
-      <c r="D484" s="15"/>
+      <c r="D484" s="16"/>
       <c r="E484" s="10"/>
       <c r="F484" s="10"/>
       <c r="G484" s="11"/>
@@ -7348,7 +7351,7 @@
       <c r="A485" s="7"/>
       <c r="B485" s="8"/>
       <c r="C485" s="9"/>
-      <c r="D485" s="15"/>
+      <c r="D485" s="16"/>
       <c r="E485" s="10"/>
       <c r="F485" s="10"/>
       <c r="G485" s="11"/>
@@ -7362,7 +7365,7 @@
       <c r="A486" s="7"/>
       <c r="B486" s="8"/>
       <c r="C486" s="9"/>
-      <c r="D486" s="15"/>
+      <c r="D486" s="16"/>
       <c r="E486" s="10"/>
       <c r="F486" s="10"/>
       <c r="G486" s="11"/>
@@ -7376,7 +7379,7 @@
       <c r="A487" s="7"/>
       <c r="B487" s="8"/>
       <c r="C487" s="9"/>
-      <c r="D487" s="15"/>
+      <c r="D487" s="16"/>
       <c r="E487" s="10"/>
       <c r="F487" s="10"/>
       <c r="G487" s="11"/>
@@ -7390,7 +7393,7 @@
       <c r="A488" s="7"/>
       <c r="B488" s="8"/>
       <c r="C488" s="9"/>
-      <c r="D488" s="15"/>
+      <c r="D488" s="16"/>
       <c r="E488" s="10"/>
       <c r="F488" s="10"/>
       <c r="G488" s="11"/>
@@ -7404,7 +7407,7 @@
       <c r="A489" s="7"/>
       <c r="B489" s="8"/>
       <c r="C489" s="9"/>
-      <c r="D489" s="15"/>
+      <c r="D489" s="16"/>
       <c r="E489" s="10"/>
       <c r="F489" s="10"/>
       <c r="G489" s="11"/>
@@ -7418,7 +7421,7 @@
       <c r="A490" s="7"/>
       <c r="B490" s="8"/>
       <c r="C490" s="9"/>
-      <c r="D490" s="15"/>
+      <c r="D490" s="16"/>
       <c r="E490" s="10"/>
       <c r="F490" s="10"/>
       <c r="G490" s="11"/>
@@ -7432,7 +7435,7 @@
       <c r="A491" s="7"/>
       <c r="B491" s="8"/>
       <c r="C491" s="9"/>
-      <c r="D491" s="15"/>
+      <c r="D491" s="16"/>
       <c r="E491" s="10"/>
       <c r="F491" s="10"/>
       <c r="G491" s="11"/>
@@ -7446,7 +7449,7 @@
       <c r="A492" s="7"/>
       <c r="B492" s="8"/>
       <c r="C492" s="9"/>
-      <c r="D492" s="15"/>
+      <c r="D492" s="16"/>
       <c r="E492" s="10"/>
       <c r="F492" s="10"/>
       <c r="G492" s="11"/>
@@ -7460,7 +7463,7 @@
       <c r="A493" s="7"/>
       <c r="B493" s="8"/>
       <c r="C493" s="9"/>
-      <c r="D493" s="15"/>
+      <c r="D493" s="16"/>
       <c r="E493" s="10"/>
       <c r="F493" s="10"/>
       <c r="G493" s="11"/>
@@ -7474,7 +7477,7 @@
       <c r="A494" s="7"/>
       <c r="B494" s="8"/>
       <c r="C494" s="9"/>
-      <c r="D494" s="15"/>
+      <c r="D494" s="16"/>
       <c r="E494" s="10"/>
       <c r="F494" s="10"/>
       <c r="G494" s="11"/>
@@ -7488,7 +7491,7 @@
       <c r="A495" s="7"/>
       <c r="B495" s="8"/>
       <c r="C495" s="9"/>
-      <c r="D495" s="15"/>
+      <c r="D495" s="16"/>
       <c r="E495" s="10"/>
       <c r="F495" s="10"/>
       <c r="G495" s="11"/>
@@ -7502,7 +7505,7 @@
       <c r="A496" s="7"/>
       <c r="B496" s="8"/>
       <c r="C496" s="9"/>
-      <c r="D496" s="15"/>
+      <c r="D496" s="16"/>
       <c r="E496" s="10"/>
       <c r="F496" s="10"/>
       <c r="G496" s="11"/>
@@ -7516,7 +7519,7 @@
       <c r="A497" s="7"/>
       <c r="B497" s="8"/>
       <c r="C497" s="9"/>
-      <c r="D497" s="15"/>
+      <c r="D497" s="16"/>
       <c r="E497" s="10"/>
       <c r="F497" s="10"/>
       <c r="G497" s="11"/>
@@ -7530,7 +7533,7 @@
       <c r="A498" s="7"/>
       <c r="B498" s="8"/>
       <c r="C498" s="9"/>
-      <c r="D498" s="15"/>
+      <c r="D498" s="16"/>
       <c r="E498" s="10"/>
       <c r="F498" s="10"/>
       <c r="G498" s="11"/>
@@ -7544,7 +7547,7 @@
       <c r="A499" s="7"/>
       <c r="B499" s="8"/>
       <c r="C499" s="9"/>
-      <c r="D499" s="15"/>
+      <c r="D499" s="16"/>
       <c r="E499" s="10"/>
       <c r="F499" s="10"/>
       <c r="G499" s="11"/>
@@ -7558,7 +7561,7 @@
       <c r="A500" s="7"/>
       <c r="B500" s="8"/>
       <c r="C500" s="9"/>
-      <c r="D500" s="15"/>
+      <c r="D500" s="16"/>
       <c r="E500" s="10"/>
       <c r="F500" s="10"/>
       <c r="G500" s="11"/>
@@ -7572,7 +7575,7 @@
       <c r="A501" s="7"/>
       <c r="B501" s="8"/>
       <c r="C501" s="9"/>
-      <c r="D501" s="15"/>
+      <c r="D501" s="16"/>
       <c r="E501" s="10"/>
       <c r="F501" s="10"/>
       <c r="G501" s="11"/>
@@ -7586,7 +7589,7 @@
       <c r="A502" s="7"/>
       <c r="B502" s="8"/>
       <c r="C502" s="9"/>
-      <c r="D502" s="15"/>
+      <c r="D502" s="16"/>
       <c r="E502" s="10"/>
       <c r="F502" s="10"/>
       <c r="G502" s="11"/>
@@ -7600,7 +7603,7 @@
       <c r="A503" s="7"/>
       <c r="B503" s="8"/>
       <c r="C503" s="9"/>
-      <c r="D503" s="15"/>
+      <c r="D503" s="16"/>
       <c r="E503" s="10"/>
       <c r="F503" s="10"/>
       <c r="G503" s="11"/>
@@ -7614,7 +7617,7 @@
       <c r="A504" s="7"/>
       <c r="B504" s="8"/>
       <c r="C504" s="9"/>
-      <c r="D504" s="15"/>
+      <c r="D504" s="16"/>
       <c r="E504" s="10"/>
       <c r="F504" s="10"/>
       <c r="G504" s="11"/>
@@ -7628,7 +7631,7 @@
       <c r="A505" s="7"/>
       <c r="B505" s="8"/>
       <c r="C505" s="9"/>
-      <c r="D505" s="15"/>
+      <c r="D505" s="16"/>
       <c r="E505" s="10"/>
       <c r="F505" s="10"/>
       <c r="G505" s="11"/>
@@ -7642,7 +7645,7 @@
       <c r="A506" s="7"/>
       <c r="B506" s="8"/>
       <c r="C506" s="9"/>
-      <c r="D506" s="15"/>
+      <c r="D506" s="16"/>
       <c r="E506" s="10"/>
       <c r="F506" s="10"/>
       <c r="G506" s="11"/>
@@ -7656,7 +7659,7 @@
       <c r="A507" s="7"/>
       <c r="B507" s="8"/>
       <c r="C507" s="9"/>
-      <c r="D507" s="15"/>
+      <c r="D507" s="16"/>
       <c r="E507" s="10"/>
       <c r="F507" s="10"/>
       <c r="G507" s="11"/>
@@ -7670,7 +7673,7 @@
       <c r="A508" s="7"/>
       <c r="B508" s="8"/>
       <c r="C508" s="9"/>
-      <c r="D508" s="15"/>
+      <c r="D508" s="16"/>
       <c r="E508" s="10"/>
       <c r="F508" s="10"/>
       <c r="G508" s="11"/>
@@ -7684,7 +7687,7 @@
       <c r="A509" s="7"/>
       <c r="B509" s="8"/>
       <c r="C509" s="9"/>
-      <c r="D509" s="15"/>
+      <c r="D509" s="16"/>
       <c r="E509" s="10"/>
       <c r="F509" s="10"/>
       <c r="G509" s="11"/>
@@ -7698,7 +7701,7 @@
       <c r="A510" s="7"/>
       <c r="B510" s="8"/>
       <c r="C510" s="9"/>
-      <c r="D510" s="15"/>
+      <c r="D510" s="16"/>
       <c r="E510" s="10"/>
       <c r="F510" s="10"/>
       <c r="G510" s="11"/>
@@ -7712,7 +7715,7 @@
       <c r="A511" s="7"/>
       <c r="B511" s="8"/>
       <c r="C511" s="9"/>
-      <c r="D511" s="15"/>
+      <c r="D511" s="16"/>
       <c r="E511" s="10"/>
       <c r="F511" s="10"/>
       <c r="G511" s="11"/>
@@ -7726,7 +7729,7 @@
       <c r="A512" s="7"/>
       <c r="B512" s="8"/>
       <c r="C512" s="9"/>
-      <c r="D512" s="15"/>
+      <c r="D512" s="16"/>
       <c r="E512" s="10"/>
       <c r="F512" s="10"/>
       <c r="G512" s="11"/>
@@ -7740,7 +7743,7 @@
       <c r="A513" s="7"/>
       <c r="B513" s="8"/>
       <c r="C513" s="9"/>
-      <c r="D513" s="15"/>
+      <c r="D513" s="16"/>
       <c r="E513" s="10"/>
       <c r="F513" s="10"/>
       <c r="G513" s="11"/>
@@ -7754,7 +7757,7 @@
       <c r="A514" s="7"/>
       <c r="B514" s="8"/>
       <c r="C514" s="9"/>
-      <c r="D514" s="15"/>
+      <c r="D514" s="16"/>
       <c r="E514" s="10"/>
       <c r="F514" s="10"/>
       <c r="G514" s="11"/>
@@ -7768,7 +7771,7 @@
       <c r="A515" s="7"/>
       <c r="B515" s="8"/>
       <c r="C515" s="9"/>
-      <c r="D515" s="15"/>
+      <c r="D515" s="16"/>
       <c r="E515" s="10"/>
       <c r="F515" s="10"/>
       <c r="G515" s="11"/>
@@ -7782,7 +7785,7 @@
       <c r="A516" s="7"/>
       <c r="B516" s="8"/>
       <c r="C516" s="9"/>
-      <c r="D516" s="15"/>
+      <c r="D516" s="16"/>
       <c r="E516" s="10"/>
       <c r="F516" s="10"/>
       <c r="G516" s="11"/>
@@ -7796,7 +7799,7 @@
       <c r="A517" s="7"/>
       <c r="B517" s="8"/>
       <c r="C517" s="9"/>
-      <c r="D517" s="15"/>
+      <c r="D517" s="16"/>
       <c r="E517" s="10"/>
       <c r="F517" s="10"/>
       <c r="G517" s="11"/>
@@ -7810,7 +7813,7 @@
       <c r="A518" s="7"/>
       <c r="B518" s="8"/>
       <c r="C518" s="9"/>
-      <c r="D518" s="15"/>
+      <c r="D518" s="16"/>
       <c r="E518" s="10"/>
       <c r="F518" s="10"/>
       <c r="G518" s="11"/>
@@ -7824,7 +7827,7 @@
       <c r="A519" s="7"/>
       <c r="B519" s="8"/>
       <c r="C519" s="9"/>
-      <c r="D519" s="15"/>
+      <c r="D519" s="16"/>
       <c r="E519" s="10"/>
       <c r="F519" s="10"/>
       <c r="G519" s="11"/>
@@ -7838,7 +7841,7 @@
       <c r="A520" s="7"/>
       <c r="B520" s="8"/>
       <c r="C520" s="9"/>
-      <c r="D520" s="15"/>
+      <c r="D520" s="16"/>
       <c r="E520" s="10"/>
       <c r="F520" s="10"/>
       <c r="G520" s="11"/>
@@ -7852,7 +7855,7 @@
       <c r="A521" s="7"/>
       <c r="B521" s="8"/>
       <c r="C521" s="9"/>
-      <c r="D521" s="15"/>
+      <c r="D521" s="16"/>
       <c r="E521" s="10"/>
       <c r="F521" s="10"/>
       <c r="G521" s="11"/>
@@ -7866,7 +7869,7 @@
       <c r="A522" s="7"/>
       <c r="B522" s="8"/>
       <c r="C522" s="9"/>
-      <c r="D522" s="15"/>
+      <c r="D522" s="16"/>
       <c r="E522" s="10"/>
       <c r="F522" s="10"/>
       <c r="G522" s="11"/>
@@ -7880,7 +7883,7 @@
       <c r="A523" s="7"/>
       <c r="B523" s="8"/>
       <c r="C523" s="9"/>
-      <c r="D523" s="15"/>
+      <c r="D523" s="16"/>
       <c r="E523" s="10"/>
       <c r="F523" s="10"/>
       <c r="G523" s="11"/>
@@ -7894,7 +7897,7 @@
       <c r="A524" s="7"/>
       <c r="B524" s="8"/>
       <c r="C524" s="9"/>
-      <c r="D524" s="15"/>
+      <c r="D524" s="16"/>
       <c r="E524" s="10"/>
       <c r="F524" s="10"/>
       <c r="G524" s="11"/>
@@ -7908,7 +7911,7 @@
       <c r="A525" s="7"/>
       <c r="B525" s="8"/>
       <c r="C525" s="9"/>
-      <c r="D525" s="15"/>
+      <c r="D525" s="16"/>
       <c r="E525" s="10"/>
       <c r="F525" s="10"/>
       <c r="G525" s="11"/>
@@ -7922,7 +7925,7 @@
       <c r="A526" s="7"/>
       <c r="B526" s="8"/>
       <c r="C526" s="9"/>
-      <c r="D526" s="15"/>
+      <c r="D526" s="16"/>
       <c r="E526" s="10"/>
       <c r="F526" s="10"/>
       <c r="G526" s="11"/>
@@ -7936,7 +7939,7 @@
       <c r="A527" s="7"/>
       <c r="B527" s="8"/>
       <c r="C527" s="9"/>
-      <c r="D527" s="15"/>
+      <c r="D527" s="16"/>
       <c r="E527" s="10"/>
       <c r="F527" s="10"/>
       <c r="G527" s="11"/>
@@ -7950,7 +7953,7 @@
       <c r="A528" s="7"/>
       <c r="B528" s="8"/>
       <c r="C528" s="9"/>
-      <c r="D528" s="15"/>
+      <c r="D528" s="16"/>
       <c r="E528" s="10"/>
       <c r="F528" s="10"/>
       <c r="G528" s="11"/>
@@ -7964,7 +7967,7 @@
       <c r="A529" s="7"/>
       <c r="B529" s="8"/>
       <c r="C529" s="9"/>
-      <c r="D529" s="15"/>
+      <c r="D529" s="16"/>
       <c r="E529" s="10"/>
       <c r="F529" s="10"/>
       <c r="G529" s="11"/>
@@ -7978,7 +7981,7 @@
       <c r="A530" s="7"/>
       <c r="B530" s="8"/>
       <c r="C530" s="9"/>
-      <c r="D530" s="15"/>
+      <c r="D530" s="16"/>
       <c r="E530" s="10"/>
       <c r="F530" s="10"/>
       <c r="G530" s="11"/>
@@ -7992,7 +7995,7 @@
       <c r="A531" s="7"/>
       <c r="B531" s="8"/>
       <c r="C531" s="9"/>
-      <c r="D531" s="15"/>
+      <c r="D531" s="16"/>
       <c r="E531" s="10"/>
       <c r="F531" s="10"/>
       <c r="G531" s="11"/>
@@ -8006,7 +8009,7 @@
       <c r="A532" s="7"/>
       <c r="B532" s="8"/>
       <c r="C532" s="9"/>
-      <c r="D532" s="15"/>
+      <c r="D532" s="16"/>
       <c r="E532" s="10"/>
       <c r="F532" s="10"/>
       <c r="G532" s="11"/>
@@ -8020,7 +8023,7 @@
       <c r="A533" s="7"/>
       <c r="B533" s="8"/>
       <c r="C533" s="9"/>
-      <c r="D533" s="15"/>
+      <c r="D533" s="16"/>
       <c r="E533" s="10"/>
       <c r="F533" s="10"/>
       <c r="G533" s="11"/>
@@ -8034,7 +8037,7 @@
       <c r="A534" s="7"/>
       <c r="B534" s="8"/>
       <c r="C534" s="9"/>
-      <c r="D534" s="15"/>
+      <c r="D534" s="16"/>
       <c r="E534" s="10"/>
       <c r="F534" s="10"/>
       <c r="G534" s="11"/>
@@ -8048,7 +8051,7 @@
       <c r="A535" s="7"/>
       <c r="B535" s="8"/>
       <c r="C535" s="9"/>
-      <c r="D535" s="15"/>
+      <c r="D535" s="16"/>
       <c r="E535" s="10"/>
       <c r="F535" s="10"/>
       <c r="G535" s="11"/>
@@ -8062,7 +8065,7 @@
       <c r="A536" s="7"/>
       <c r="B536" s="8"/>
       <c r="C536" s="9"/>
-      <c r="D536" s="15"/>
+      <c r="D536" s="16"/>
       <c r="E536" s="10"/>
       <c r="F536" s="10"/>
       <c r="G536" s="11"/>
@@ -8076,7 +8079,7 @@
       <c r="A537" s="7"/>
       <c r="B537" s="8"/>
       <c r="C537" s="9"/>
-      <c r="D537" s="15"/>
+      <c r="D537" s="16"/>
       <c r="E537" s="10"/>
       <c r="F537" s="10"/>
       <c r="G537" s="11"/>
@@ -8090,7 +8093,7 @@
       <c r="A538" s="7"/>
       <c r="B538" s="8"/>
       <c r="C538" s="9"/>
-      <c r="D538" s="15"/>
+      <c r="D538" s="16"/>
       <c r="E538" s="10"/>
       <c r="F538" s="10"/>
       <c r="G538" s="11"/>
@@ -8104,7 +8107,7 @@
       <c r="A539" s="7"/>
       <c r="B539" s="8"/>
       <c r="C539" s="9"/>
-      <c r="D539" s="15"/>
+      <c r="D539" s="16"/>
       <c r="E539" s="10"/>
       <c r="F539" s="10"/>
       <c r="G539" s="11"/>
@@ -8118,7 +8121,7 @@
       <c r="A540" s="7"/>
       <c r="B540" s="8"/>
       <c r="C540" s="9"/>
-      <c r="D540" s="15"/>
+      <c r="D540" s="16"/>
       <c r="E540" s="10"/>
       <c r="F540" s="10"/>
       <c r="G540" s="11"/>
@@ -8132,7 +8135,7 @@
       <c r="A541" s="7"/>
       <c r="B541" s="8"/>
       <c r="C541" s="9"/>
-      <c r="D541" s="15"/>
+      <c r="D541" s="16"/>
       <c r="E541" s="10"/>
       <c r="F541" s="10"/>
       <c r="G541" s="11"/>
@@ -8146,7 +8149,7 @@
       <c r="A542" s="7"/>
       <c r="B542" s="8"/>
       <c r="C542" s="9"/>
-      <c r="D542" s="15"/>
+      <c r="D542" s="16"/>
       <c r="E542" s="10"/>
       <c r="F542" s="10"/>
       <c r="G542" s="11"/>
@@ -8160,7 +8163,7 @@
       <c r="A543" s="7"/>
       <c r="B543" s="8"/>
       <c r="C543" s="9"/>
-      <c r="D543" s="15"/>
+      <c r="D543" s="16"/>
       <c r="E543" s="10"/>
       <c r="F543" s="10"/>
       <c r="G543" s="11"/>
@@ -8174,7 +8177,7 @@
       <c r="A544" s="7"/>
       <c r="B544" s="8"/>
       <c r="C544" s="9"/>
-      <c r="D544" s="15"/>
+      <c r="D544" s="16"/>
       <c r="E544" s="10"/>
       <c r="F544" s="10"/>
       <c r="G544" s="11"/>
@@ -8188,7 +8191,7 @@
       <c r="A545" s="7"/>
       <c r="B545" s="8"/>
       <c r="C545" s="9"/>
-      <c r="D545" s="15"/>
+      <c r="D545" s="16"/>
       <c r="E545" s="10"/>
       <c r="F545" s="10"/>
       <c r="G545" s="11"/>
@@ -8202,7 +8205,7 @@
       <c r="A546" s="7"/>
       <c r="B546" s="8"/>
       <c r="C546" s="9"/>
-      <c r="D546" s="15"/>
+      <c r="D546" s="16"/>
       <c r="E546" s="10"/>
       <c r="F546" s="10"/>
       <c r="G546" s="11"/>
@@ -8216,7 +8219,7 @@
       <c r="A547" s="7"/>
       <c r="B547" s="8"/>
       <c r="C547" s="9"/>
-      <c r="D547" s="15"/>
+      <c r="D547" s="16"/>
       <c r="E547" s="10"/>
       <c r="F547" s="10"/>
       <c r="G547" s="11"/>
@@ -8230,7 +8233,7 @@
       <c r="A548" s="7"/>
       <c r="B548" s="8"/>
       <c r="C548" s="9"/>
-      <c r="D548" s="15"/>
+      <c r="D548" s="16"/>
       <c r="E548" s="10"/>
       <c r="F548" s="10"/>
       <c r="G548" s="11"/>
@@ -8244,7 +8247,7 @@
       <c r="A549" s="7"/>
       <c r="B549" s="8"/>
       <c r="C549" s="9"/>
-      <c r="D549" s="15"/>
+      <c r="D549" s="16"/>
       <c r="E549" s="10"/>
       <c r="F549" s="10"/>
       <c r="G549" s="11"/>
@@ -8258,7 +8261,7 @@
       <c r="A550" s="7"/>
       <c r="B550" s="8"/>
       <c r="C550" s="9"/>
-      <c r="D550" s="15"/>
+      <c r="D550" s="16"/>
       <c r="E550" s="10"/>
       <c r="F550" s="10"/>
       <c r="G550" s="11"/>
@@ -8272,7 +8275,7 @@
       <c r="A551" s="7"/>
       <c r="B551" s="8"/>
       <c r="C551" s="9"/>
-      <c r="D551" s="15"/>
+      <c r="D551" s="16"/>
       <c r="E551" s="10"/>
       <c r="F551" s="10"/>
       <c r="G551" s="11"/>
@@ -8286,7 +8289,7 @@
       <c r="A552" s="7"/>
       <c r="B552" s="8"/>
       <c r="C552" s="9"/>
-      <c r="D552" s="15"/>
+      <c r="D552" s="16"/>
       <c r="E552" s="10"/>
       <c r="F552" s="10"/>
       <c r="G552" s="11"/>
@@ -8300,7 +8303,7 @@
       <c r="A553" s="7"/>
       <c r="B553" s="8"/>
       <c r="C553" s="9"/>
-      <c r="D553" s="15"/>
+      <c r="D553" s="16"/>
       <c r="E553" s="10"/>
       <c r="F553" s="10"/>
       <c r="G553" s="11"/>
@@ -8314,7 +8317,7 @@
       <c r="A554" s="7"/>
       <c r="B554" s="8"/>
       <c r="C554" s="9"/>
-      <c r="D554" s="15"/>
+      <c r="D554" s="16"/>
       <c r="E554" s="10"/>
       <c r="F554" s="10"/>
       <c r="G554" s="11"/>
@@ -8328,7 +8331,7 @@
       <c r="A555" s="7"/>
       <c r="B555" s="8"/>
       <c r="C555" s="9"/>
-      <c r="D555" s="15"/>
+      <c r="D555" s="16"/>
       <c r="E555" s="10"/>
       <c r="F555" s="10"/>
       <c r="G555" s="11"/>
@@ -8342,7 +8345,7 @@
       <c r="A556" s="7"/>
       <c r="B556" s="8"/>
       <c r="C556" s="9"/>
-      <c r="D556" s="15"/>
+      <c r="D556" s="16"/>
       <c r="E556" s="10"/>
       <c r="F556" s="10"/>
       <c r="G556" s="11"/>
@@ -8356,7 +8359,7 @@
       <c r="A557" s="7"/>
       <c r="B557" s="8"/>
       <c r="C557" s="9"/>
-      <c r="D557" s="15"/>
+      <c r="D557" s="16"/>
       <c r="E557" s="10"/>
       <c r="F557" s="10"/>
       <c r="G557" s="11"/>
@@ -8370,7 +8373,7 @@
       <c r="A558" s="7"/>
       <c r="B558" s="8"/>
       <c r="C558" s="9"/>
-      <c r="D558" s="15"/>
+      <c r="D558" s="16"/>
       <c r="E558" s="10"/>
       <c r="F558" s="10"/>
       <c r="G558" s="11"/>
@@ -8384,7 +8387,7 @@
       <c r="A559" s="7"/>
       <c r="B559" s="8"/>
       <c r="C559" s="9"/>
-      <c r="D559" s="15"/>
+      <c r="D559" s="16"/>
       <c r="E559" s="10"/>
       <c r="F559" s="10"/>
       <c r="G559" s="11"/>
@@ -8398,7 +8401,7 @@
       <c r="A560" s="7"/>
       <c r="B560" s="8"/>
       <c r="C560" s="9"/>
-      <c r="D560" s="15"/>
+      <c r="D560" s="16"/>
       <c r="E560" s="10"/>
       <c r="F560" s="10"/>
       <c r="G560" s="11"/>
@@ -8412,7 +8415,7 @@
       <c r="A561" s="7"/>
       <c r="B561" s="8"/>
       <c r="C561" s="9"/>
-      <c r="D561" s="15"/>
+      <c r="D561" s="16"/>
       <c r="E561" s="10"/>
       <c r="F561" s="10"/>
       <c r="G561" s="11"/>
@@ -8426,7 +8429,7 @@
       <c r="A562" s="7"/>
       <c r="B562" s="8"/>
       <c r="C562" s="9"/>
-      <c r="D562" s="15"/>
+      <c r="D562" s="16"/>
       <c r="E562" s="10"/>
       <c r="F562" s="10"/>
       <c r="G562" s="11"/>
@@ -8440,7 +8443,7 @@
       <c r="A563" s="7"/>
       <c r="B563" s="8"/>
       <c r="C563" s="9"/>
-      <c r="D563" s="15"/>
+      <c r="D563" s="16"/>
       <c r="E563" s="10"/>
       <c r="F563" s="10"/>
       <c r="G563" s="11"/>
@@ -8454,7 +8457,7 @@
       <c r="A564" s="7"/>
       <c r="B564" s="8"/>
       <c r="C564" s="9"/>
-      <c r="D564" s="15"/>
+      <c r="D564" s="16"/>
       <c r="E564" s="10"/>
       <c r="F564" s="10"/>
       <c r="G564" s="11"/>
@@ -8468,7 +8471,7 @@
       <c r="A565" s="7"/>
       <c r="B565" s="8"/>
       <c r="C565" s="9"/>
-      <c r="D565" s="15"/>
+      <c r="D565" s="16"/>
       <c r="E565" s="10"/>
       <c r="F565" s="10"/>
       <c r="G565" s="11"/>
@@ -8482,7 +8485,7 @@
       <c r="A566" s="7"/>
       <c r="B566" s="8"/>
       <c r="C566" s="9"/>
-      <c r="D566" s="15"/>
+      <c r="D566" s="16"/>
       <c r="E566" s="10"/>
       <c r="F566" s="10"/>
       <c r="G566" s="11"/>
@@ -8496,7 +8499,7 @@
       <c r="A567" s="7"/>
       <c r="B567" s="8"/>
       <c r="C567" s="9"/>
-      <c r="D567" s="15"/>
+      <c r="D567" s="16"/>
       <c r="E567" s="10"/>
       <c r="F567" s="10"/>
       <c r="G567" s="11"/>
@@ -8510,7 +8513,7 @@
       <c r="A568" s="7"/>
       <c r="B568" s="8"/>
       <c r="C568" s="9"/>
-      <c r="D568" s="15"/>
+      <c r="D568" s="16"/>
       <c r="E568" s="10"/>
       <c r="F568" s="10"/>
       <c r="G568" s="11"/>
@@ -8524,7 +8527,7 @@
       <c r="A569" s="7"/>
       <c r="B569" s="8"/>
       <c r="C569" s="9"/>
-      <c r="D569" s="15"/>
+      <c r="D569" s="16"/>
       <c r="E569" s="10"/>
       <c r="F569" s="10"/>
       <c r="G569" s="11"/>
@@ -8538,7 +8541,7 @@
       <c r="A570" s="7"/>
       <c r="B570" s="8"/>
       <c r="C570" s="9"/>
-      <c r="D570" s="15"/>
+      <c r="D570" s="16"/>
       <c r="E570" s="10"/>
       <c r="F570" s="10"/>
       <c r="G570" s="11"/>
